--- a/NORMATIVOS_AKC.xlsx
+++ b/NORMATIVOS_AKC.xlsx
@@ -19,7 +19,7 @@
     <sheet name="CONSOLIDADO" sheetId="3" r:id="rId4"/>
     <sheet name="CATALOGOS" sheetId="2" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31722,7 +31722,7 @@
     <mergeCell ref="AI219:AI223"/>
     <mergeCell ref="AJ219:AJ223"/>
   </mergeCells>
-  <conditionalFormatting sqref="C3:AF279">
+  <conditionalFormatting sqref="C3:XFD279">
     <cfRule type="expression" dxfId="26" priority="2">
       <formula>C3="Consolidado"</formula>
     </cfRule>
@@ -31745,7 +31745,7 @@
           <x14:formula1>
             <xm:f>CATALOGOS!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>C176:AF231 C3:AF46 C49:AF105 C108:AF142 C145:AF173 C234:AF279</xm:sqref>
+          <xm:sqref>C176:XFD231 C3:XFD46 C49:XFD105 C108:XFD142 C145:XFD173 C234:XFD279</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -31814,22 +31814,22 @@
         <v>311</v>
       </c>
       <c r="B6">
-        <f>INDEX(CONSOLIDADO!$B$4:$B$33,MATCH($B$3,CONSOLIDADO!$A$4:$A$33,0))</f>
+        <f>INDEX(CONSOLIDADO!$B$4:$B$1048576,MATCH($B$3,CONSOLIDADO!$A$4:$A$1048576,0))</f>
         <v>267</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
       </c>
       <c r="E6">
-        <f>--(INDEX(NORMATIVOS!$C$3:$AF$3,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$4:$AF$4,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$5:$AF$5,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$6:$AF$6,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$7:$AF$7,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$8:$AF$8,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$9:$AF$9,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$10:$AF$10,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$11:$AF$11,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$12:$AF$12,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$13:$AF$13,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$14:$AF$14,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$15:$AF$15,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$16:$AF$16,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")</f>
+        <f>--(INDEX(NORMATIVOS!$C$3:$XFD$3,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$4:$XFD$4,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$5:$XFD$5,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$6:$XFD$6,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$7:$XFD$7,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$8:$XFD$8,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$9:$XFD$9,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$10:$XFD$10,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$11:$XFD$11,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$12:$XFD$12,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$13:$XFD$13,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$14:$XFD$14,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$15:$XFD$15,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$16:$XFD$16,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")</f>
         <v>13</v>
       </c>
       <c r="F6">
-        <f>--(INDEX(NORMATIVOS!$C$3:$AF$3,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$4:$AF$4,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$5:$AF$5,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$6:$AF$6,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$7:$AF$7,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$8:$AF$8,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$9:$AF$9,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$10:$AF$10,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$11:$AF$11,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$12:$AF$12,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$13:$AF$13,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$14:$AF$14,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$15:$AF$15,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$16:$AF$16,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")</f>
+        <f>--(INDEX(NORMATIVOS!$C$3:$XFD$3,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$4:$XFD$4,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$5:$XFD$5,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$6:$XFD$6,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$7:$XFD$7,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$8:$XFD$8,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$9:$XFD$9,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$10:$XFD$10,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$11:$XFD$11,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$12:$XFD$12,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$13:$XFD$13,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$14:$XFD$14,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$15:$XFD$15,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$16:$XFD$16,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")</f>
         <v>1</v>
       </c>
       <c r="G6">
-        <f>--(INDEX(NORMATIVOS!$C$3:$AF$3,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$4:$AF$4,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$5:$AF$5,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$6:$AF$6,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$7:$AF$7,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$8:$AF$8,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$9:$AF$9,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$10:$AF$10,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$11:$AF$11,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$12:$AF$12,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$13:$AF$13,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$14:$AF$14,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$15:$AF$15,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$16:$AF$16,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")</f>
+        <f>--(INDEX(NORMATIVOS!$C$3:$XFD$3,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$4:$XFD$4,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$5:$XFD$5,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$6:$XFD$6,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$7:$XFD$7,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$8:$XFD$8,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$9:$XFD$9,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$10:$XFD$10,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$11:$XFD$11,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$12:$XFD$12,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$13:$XFD$13,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$14:$XFD$14,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$15:$XFD$15,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$16:$XFD$16,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")</f>
         <v>0</v>
       </c>
       <c r="H6" s="13">
@@ -31842,22 +31842,22 @@
         <v>312</v>
       </c>
       <c r="B7">
-        <f>INDEX(CONSOLIDADO!$C$4:$C$33,MATCH($B$3,CONSOLIDADO!$A$4:$A$33,0))</f>
+        <f>INDEX(CONSOLIDADO!$C$4:$C$1048576,MATCH($B$3,CONSOLIDADO!$A$4:$A$1048576,0))</f>
         <v>144</v>
       </c>
       <c r="D7" t="s">
         <v>301</v>
       </c>
       <c r="E7">
-        <f>--(INDEX(NORMATIVOS!$C$17:$AF$17,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$18:$AF$18,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$19:$AF$19,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$20:$AF$20,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$21:$AF$21,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$22:$AF$22,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$23:$AF$23,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$24:$AF$24,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$25:$AF$25,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$26:$AF$26,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$27:$AF$27,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")</f>
+        <f>--(INDEX(NORMATIVOS!$C$17:$XFD$17,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$18:$XFD$18,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$19:$XFD$19,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$20:$XFD$20,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$21:$XFD$21,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$22:$XFD$22,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$23:$XFD$23,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$24:$XFD$24,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$25:$XFD$25,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$26:$XFD$26,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$27:$XFD$27,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")</f>
         <v>9</v>
       </c>
       <c r="F7">
-        <f>--(INDEX(NORMATIVOS!$C$17:$AF$17,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$18:$AF$18,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$19:$AF$19,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$20:$AF$20,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$21:$AF$21,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$22:$AF$22,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$23:$AF$23,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$24:$AF$24,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$25:$AF$25,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$26:$AF$26,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$27:$AF$27,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")</f>
+        <f>--(INDEX(NORMATIVOS!$C$17:$XFD$17,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$18:$XFD$18,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$19:$XFD$19,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$20:$XFD$20,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$21:$XFD$21,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$22:$XFD$22,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$23:$XFD$23,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$24:$XFD$24,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$25:$XFD$25,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$26:$XFD$26,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$27:$XFD$27,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")</f>
         <v>1</v>
       </c>
       <c r="G7">
-        <f>--(INDEX(NORMATIVOS!$C$17:$AF$17,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$18:$AF$18,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$19:$AF$19,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$20:$AF$20,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$21:$AF$21,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$22:$AF$22,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$23:$AF$23,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$24:$AF$24,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$25:$AF$25,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$26:$AF$26,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$27:$AF$27,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")</f>
+        <f>--(INDEX(NORMATIVOS!$C$17:$XFD$17,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$18:$XFD$18,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$19:$XFD$19,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$20:$XFD$20,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$21:$XFD$21,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$22:$XFD$22,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$23:$XFD$23,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$24:$XFD$24,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$25:$XFD$25,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$26:$XFD$26,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$27:$XFD$27,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")</f>
         <v>1</v>
       </c>
       <c r="H7" s="13">
@@ -31870,22 +31870,22 @@
         <v>303</v>
       </c>
       <c r="B8">
-        <f>INDEX(CONSOLIDADO!$D$4:$D$33,MATCH($B$3,CONSOLIDADO!$A$4:$A$33,0))</f>
+        <f>INDEX(CONSOLIDADO!$D$4:$D$1048576,MATCH($B$3,CONSOLIDADO!$A$4:$A$1048576,0))</f>
         <v>36</v>
       </c>
       <c r="D8" t="s">
         <v>304</v>
       </c>
       <c r="E8">
-        <f>--(INDEX(NORMATIVOS!$C$28:$AF$28,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$29:$AF$29,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$30:$AF$30,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$31:$AF$31,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$32:$AF$32,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$33:$AF$33,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$34:$AF$34,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$35:$AF$35,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$36:$AF$36,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$37:$AF$37,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")</f>
+        <f>--(INDEX(NORMATIVOS!$C$28:$XFD$28,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$29:$XFD$29,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$30:$XFD$30,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$31:$XFD$31,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$32:$XFD$32,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$33:$XFD$33,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$34:$XFD$34,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$35:$XFD$35,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$36:$XFD$36,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$37:$XFD$37,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")</f>
         <v>8</v>
       </c>
       <c r="F8">
-        <f>--(INDEX(NORMATIVOS!$C$28:$AF$28,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$29:$AF$29,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$30:$AF$30,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$31:$AF$31,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$32:$AF$32,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$33:$AF$33,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$34:$AF$34,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$35:$AF$35,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$36:$AF$36,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$37:$AF$37,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")</f>
+        <f>--(INDEX(NORMATIVOS!$C$28:$XFD$28,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$29:$XFD$29,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$30:$XFD$30,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$31:$XFD$31,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$32:$XFD$32,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$33:$XFD$33,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$34:$XFD$34,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$35:$XFD$35,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$36:$XFD$36,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$37:$XFD$37,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")</f>
         <v>1</v>
       </c>
       <c r="G8">
-        <f>--(INDEX(NORMATIVOS!$C$28:$AF$28,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$29:$AF$29,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$30:$AF$30,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$31:$AF$31,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$32:$AF$32,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$33:$AF$33,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$34:$AF$34,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$35:$AF$35,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$36:$AF$36,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$37:$AF$37,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")</f>
+        <f>--(INDEX(NORMATIVOS!$C$28:$XFD$28,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$29:$XFD$29,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$30:$XFD$30,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$31:$XFD$31,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$32:$XFD$32,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$33:$XFD$33,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$34:$XFD$34,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$35:$XFD$35,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$36:$XFD$36,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$37:$XFD$37,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")</f>
         <v>0</v>
       </c>
       <c r="H8" s="13">
@@ -31898,22 +31898,22 @@
         <v>34</v>
       </c>
       <c r="B9">
-        <f>INDEX(CONSOLIDADO!$E$4:$E$33,MATCH($B$3,CONSOLIDADO!$A$4:$A$33,0))</f>
+        <f>INDEX(CONSOLIDADO!$E$4:$E$1048576,MATCH($B$3,CONSOLIDADO!$A$4:$A$1048576,0))</f>
         <v>78</v>
       </c>
       <c r="D9" t="s">
         <v>306</v>
       </c>
       <c r="E9">
-        <f>--(INDEX(NORMATIVOS!$C$38:$AF$38,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$39:$AF$39,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$40:$AF$40,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$41:$AF$41,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$42:$AF$42,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$43:$AF$43,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$44:$AF$44,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$45:$AF$45,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$46:$AF$46,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")</f>
+        <f>--(INDEX(NORMATIVOS!$C$38:$XFD$38,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$39:$XFD$39,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$40:$XFD$40,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$41:$XFD$41,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$42:$XFD$42,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$43:$XFD$43,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$44:$XFD$44,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$45:$XFD$45,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$46:$XFD$46,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")</f>
         <v>4</v>
       </c>
       <c r="F9">
-        <f>--(INDEX(NORMATIVOS!$C$38:$AF$38,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$39:$AF$39,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$40:$AF$40,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$41:$AF$41,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$42:$AF$42,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$43:$AF$43,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$44:$AF$44,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$45:$AF$45,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$46:$AF$46,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")</f>
+        <f>--(INDEX(NORMATIVOS!$C$38:$XFD$38,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$39:$XFD$39,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$40:$XFD$40,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$41:$XFD$41,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$42:$XFD$42,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$43:$XFD$43,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$44:$XFD$44,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$45:$XFD$45,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$46:$XFD$46,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")</f>
         <v>4</v>
       </c>
       <c r="G9">
-        <f>--(INDEX(NORMATIVOS!$C$38:$AF$38,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$39:$AF$39,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$40:$AF$40,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$41:$AF$41,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$42:$AF$42,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$43:$AF$43,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$44:$AF$44,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$45:$AF$45,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$46:$AF$46,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")</f>
+        <f>--(INDEX(NORMATIVOS!$C$38:$XFD$38,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$39:$XFD$39,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$40:$XFD$40,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$41:$XFD$41,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$42:$XFD$42,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$43:$XFD$43,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$44:$XFD$44,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$45:$XFD$45,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$46:$XFD$46,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")</f>
         <v>1</v>
       </c>
       <c r="H9" s="13">
@@ -31926,22 +31926,22 @@
         <v>299</v>
       </c>
       <c r="B10">
-        <f>INDEX(CONSOLIDADO!$F$4:$F$33,MATCH($B$3,CONSOLIDADO!$A$4:$A$33,0))</f>
+        <f>INDEX(CONSOLIDADO!$F$4:$F$1048576,MATCH($B$3,CONSOLIDADO!$A$4:$A$1048576,0))</f>
         <v>9</v>
       </c>
       <c r="D10" t="s">
         <v>82</v>
       </c>
       <c r="E10">
-        <f>--(INDEX(NORMATIVOS!$C$49:$AF$49,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$50:$AF$50,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$51:$AF$51,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$52:$AF$52,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$53:$AF$53,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$54:$AF$54,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$55:$AF$55,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$56:$AF$56,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$57:$AF$57,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$58:$AF$58,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$59:$AF$59,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$60:$AF$60,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$61:$AF$61,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$62:$AF$62,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$63:$AF$63,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$64:$AF$64,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")</f>
+        <f>--(INDEX(NORMATIVOS!$C$49:$XFD$49,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$50:$XFD$50,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$51:$XFD$51,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$52:$XFD$52,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$53:$XFD$53,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$54:$XFD$54,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$55:$XFD$55,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$56:$XFD$56,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$57:$XFD$57,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$58:$XFD$58,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$59:$XFD$59,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$60:$XFD$60,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$61:$XFD$61,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$62:$XFD$62,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$63:$XFD$63,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$64:$XFD$64,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")</f>
         <v>16</v>
       </c>
       <c r="F10">
-        <f>--(INDEX(NORMATIVOS!$C$49:$AF$49,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$50:$AF$50,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$51:$AF$51,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$52:$AF$52,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$53:$AF$53,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$54:$AF$54,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$55:$AF$55,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$56:$AF$56,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$57:$AF$57,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$58:$AF$58,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$59:$AF$59,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$60:$AF$60,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$61:$AF$61,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$62:$AF$62,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$63:$AF$63,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$64:$AF$64,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")</f>
+        <f>--(INDEX(NORMATIVOS!$C$49:$XFD$49,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$50:$XFD$50,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$51:$XFD$51,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$52:$XFD$52,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$53:$XFD$53,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$54:$XFD$54,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$55:$XFD$55,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$56:$XFD$56,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$57:$XFD$57,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$58:$XFD$58,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$59:$XFD$59,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$60:$XFD$60,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$61:$XFD$61,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$62:$XFD$62,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$63:$XFD$63,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$64:$XFD$64,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")</f>
         <v>0</v>
       </c>
       <c r="G10">
-        <f>--(INDEX(NORMATIVOS!$C$49:$AF$49,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$50:$AF$50,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$51:$AF$51,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$52:$AF$52,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$53:$AF$53,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$54:$AF$54,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$55:$AF$55,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$56:$AF$56,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$57:$AF$57,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$58:$AF$58,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$59:$AF$59,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$60:$AF$60,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$61:$AF$61,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$62:$AF$62,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$63:$AF$63,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$64:$AF$64,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")</f>
+        <f>--(INDEX(NORMATIVOS!$C$49:$XFD$49,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$50:$XFD$50,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$51:$XFD$51,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$52:$XFD$52,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$53:$XFD$53,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$54:$XFD$54,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$55:$XFD$55,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$56:$XFD$56,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$57:$XFD$57,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$58:$XFD$58,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$59:$XFD$59,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$60:$XFD$60,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$61:$XFD$61,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$62:$XFD$62,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$63:$XFD$63,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$64:$XFD$64,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")</f>
         <v>0</v>
       </c>
       <c r="H10" s="13">
@@ -31954,22 +31954,22 @@
         <v>313</v>
       </c>
       <c r="B11" s="13">
-        <f>INDEX(CONSOLIDADO!$G$4:$G$33,MATCH($B$3,CONSOLIDADO!$A$4:$A$33,0))</f>
+        <f>INDEX(CONSOLIDADO!$G$4:$G$1048576,MATCH($B$3,CONSOLIDADO!$A$4:$A$1048576,0))</f>
         <v>0.55813953488372092</v>
       </c>
       <c r="D11" t="s">
         <v>99</v>
       </c>
       <c r="E11">
-        <f>--(INDEX(NORMATIVOS!$C$65:$AF$65,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$66:$AF$66,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$67:$AF$67,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$68:$AF$68,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$69:$AF$69,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$70:$AF$70,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$71:$AF$71,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$72:$AF$72,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$73:$AF$73,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$74:$AF$74,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$75:$AF$75,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$76:$AF$76,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$77:$AF$77,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$78:$AF$78,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")</f>
+        <f>--(INDEX(NORMATIVOS!$C$65:$XFD$65,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$66:$XFD$66,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$67:$XFD$67,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$68:$XFD$68,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$69:$XFD$69,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$70:$XFD$70,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$71:$XFD$71,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$72:$XFD$72,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$73:$XFD$73,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$74:$XFD$74,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$75:$XFD$75,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$76:$XFD$76,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$77:$XFD$77,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$78:$XFD$78,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")</f>
         <v>10</v>
       </c>
       <c r="F11">
-        <f>--(INDEX(NORMATIVOS!$C$65:$AF$65,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$66:$AF$66,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$67:$AF$67,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$68:$AF$68,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$69:$AF$69,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$70:$AF$70,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$71:$AF$71,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$72:$AF$72,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$73:$AF$73,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$74:$AF$74,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$75:$AF$75,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$76:$AF$76,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$77:$AF$77,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$78:$AF$78,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")</f>
+        <f>--(INDEX(NORMATIVOS!$C$65:$XFD$65,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$66:$XFD$66,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$67:$XFD$67,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$68:$XFD$68,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$69:$XFD$69,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$70:$XFD$70,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$71:$XFD$71,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$72:$XFD$72,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$73:$XFD$73,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$74:$XFD$74,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$75:$XFD$75,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$76:$XFD$76,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$77:$XFD$77,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$78:$XFD$78,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")</f>
         <v>0</v>
       </c>
       <c r="G11">
-        <f>--(INDEX(NORMATIVOS!$C$65:$AF$65,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$66:$AF$66,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$67:$AF$67,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$68:$AF$68,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$69:$AF$69,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$70:$AF$70,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$71:$AF$71,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$72:$AF$72,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$73:$AF$73,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$74:$AF$74,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$75:$AF$75,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$76:$AF$76,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$77:$AF$77,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$78:$AF$78,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")</f>
+        <f>--(INDEX(NORMATIVOS!$C$65:$XFD$65,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$66:$XFD$66,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$67:$XFD$67,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$68:$XFD$68,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$69:$XFD$69,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$70:$XFD$70,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$71:$XFD$71,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$72:$XFD$72,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$73:$XFD$73,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$74:$XFD$74,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$75:$XFD$75,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$76:$XFD$76,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$77:$XFD$77,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$78:$XFD$78,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")</f>
         <v>0</v>
       </c>
       <c r="H11" s="13">
@@ -31982,15 +31982,15 @@
         <v>109</v>
       </c>
       <c r="E12">
-        <f>--(INDEX(NORMATIVOS!$C$79:$AF$79,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$80:$AF$80,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$81:$AF$81,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$82:$AF$82,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$83:$AF$83,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$84:$AF$84,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$85:$AF$85,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$86:$AF$86,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$87:$AF$87,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$88:$AF$88,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$89:$AF$89,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$90:$AF$90,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$91:$AF$91,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$92:$AF$92,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$93:$AF$93,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$94:$AF$94,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$95:$AF$95,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$96:$AF$96,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$97:$AF$97,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$98:$AF$98,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$99:$AF$99,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$100:$AF$100,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$101:$AF$101,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$103:$AF$103,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$104:$AF$104,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$105:$AF$105,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")</f>
+        <f>--(INDEX(NORMATIVOS!$C$79:$XFD$79,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$80:$XFD$80,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$81:$XFD$81,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$82:$XFD$82,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$83:$XFD$83,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$84:$XFD$84,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$85:$XFD$85,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$86:$XFD$86,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$87:$XFD$87,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$88:$XFD$88,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$89:$XFD$89,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$90:$XFD$90,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$91:$XFD$91,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$92:$XFD$92,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$93:$XFD$93,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$94:$XFD$94,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$95:$XFD$95,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$96:$XFD$96,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$97:$XFD$97,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$98:$XFD$98,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$99:$XFD$99,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$100:$XFD$100,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$101:$XFD$101,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$103:$XFD$103,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$104:$XFD$104,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$105:$XFD$105,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")</f>
         <v>10</v>
       </c>
       <c r="F12">
-        <f>--(INDEX(NORMATIVOS!$C$79:$AF$79,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$80:$AF$80,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$81:$AF$81,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$82:$AF$82,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$83:$AF$83,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$84:$AF$84,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$85:$AF$85,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$86:$AF$86,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$87:$AF$87,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$88:$AF$88,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$89:$AF$89,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$90:$AF$90,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$91:$AF$91,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$92:$AF$92,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$93:$AF$93,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$94:$AF$94,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$95:$AF$95,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$96:$AF$96,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$97:$AF$97,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$98:$AF$98,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$99:$AF$99,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$100:$AF$100,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$101:$AF$101,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$103:$AF$103,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$104:$AF$104,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$105:$AF$105,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")</f>
+        <f>--(INDEX(NORMATIVOS!$C$79:$XFD$79,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$80:$XFD$80,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$81:$XFD$81,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$82:$XFD$82,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$83:$XFD$83,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$84:$XFD$84,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$85:$XFD$85,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$86:$XFD$86,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$87:$XFD$87,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$88:$XFD$88,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$89:$XFD$89,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$90:$XFD$90,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$91:$XFD$91,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$92:$XFD$92,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$93:$XFD$93,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$94:$XFD$94,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$95:$XFD$95,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$96:$XFD$96,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$97:$XFD$97,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$98:$XFD$98,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$99:$XFD$99,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$100:$XFD$100,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$101:$XFD$101,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$103:$XFD$103,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$104:$XFD$104,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$105:$XFD$105,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")</f>
         <v>3</v>
       </c>
       <c r="G12">
-        <f>--(INDEX(NORMATIVOS!$C$79:$AF$79,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$80:$AF$80,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$81:$AF$81,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$82:$AF$82,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$83:$AF$83,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$84:$AF$84,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$85:$AF$85,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$86:$AF$86,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$87:$AF$87,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$88:$AF$88,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$89:$AF$89,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$90:$AF$90,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$91:$AF$91,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$92:$AF$92,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$93:$AF$93,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$94:$AF$94,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$95:$AF$95,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$96:$AF$96,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$97:$AF$97,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$98:$AF$98,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$99:$AF$99,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$100:$AF$100,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$101:$AF$101,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$103:$AF$103,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$104:$AF$104,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$105:$AF$105,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")</f>
+        <f>--(INDEX(NORMATIVOS!$C$79:$XFD$79,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$80:$XFD$80,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$81:$XFD$81,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$82:$XFD$82,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$83:$XFD$83,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$84:$XFD$84,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$85:$XFD$85,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$86:$XFD$86,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$87:$XFD$87,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$88:$XFD$88,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$89:$XFD$89,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$90:$XFD$90,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$91:$XFD$91,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$92:$XFD$92,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$93:$XFD$93,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$94:$XFD$94,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$95:$XFD$95,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$96:$XFD$96,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$97:$XFD$97,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$98:$XFD$98,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$99:$XFD$99,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$100:$XFD$100,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$101:$XFD$101,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$103:$XFD$103,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$104:$XFD$104,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$105:$XFD$105,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")</f>
         <v>13</v>
       </c>
       <c r="H12" s="13">
@@ -32003,15 +32003,15 @@
         <v>135</v>
       </c>
       <c r="E13">
-        <f>--(INDEX(NORMATIVOS!$C$108:$AF$108,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$109:$AF$109,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$110:$AF$110,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$111:$AF$111,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$112:$AF$112,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$113:$AF$113,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$114:$AF$114,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$115:$AF$115,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$116:$AF$116,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$117:$AF$117,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$118:$AF$118,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$119:$AF$119,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$120:$AF$120,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$121:$AF$121,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$122:$AF$122,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")</f>
+        <f>--(INDEX(NORMATIVOS!$C$108:$XFD$108,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$109:$XFD$109,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$110:$XFD$110,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$111:$XFD$111,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$112:$XFD$112,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$113:$XFD$113,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$114:$XFD$114,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$115:$XFD$115,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$116:$XFD$116,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$117:$XFD$117,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$118:$XFD$118,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$119:$XFD$119,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$120:$XFD$120,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$121:$XFD$121,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$122:$XFD$122,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")</f>
         <v>8</v>
       </c>
       <c r="F13">
-        <f>--(INDEX(NORMATIVOS!$C$108:$AF$108,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$109:$AF$109,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$110:$AF$110,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$111:$AF$111,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$112:$AF$112,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$113:$AF$113,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$114:$AF$114,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$115:$AF$115,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$116:$AF$116,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$117:$AF$117,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$118:$AF$118,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$119:$AF$119,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$120:$AF$120,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$121:$AF$121,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$122:$AF$122,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")</f>
+        <f>--(INDEX(NORMATIVOS!$C$108:$XFD$108,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$109:$XFD$109,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$110:$XFD$110,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$111:$XFD$111,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$112:$XFD$112,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$113:$XFD$113,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$114:$XFD$114,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$115:$XFD$115,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$116:$XFD$116,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$117:$XFD$117,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$118:$XFD$118,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$119:$XFD$119,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$120:$XFD$120,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$121:$XFD$121,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$122:$XFD$122,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")</f>
         <v>3</v>
       </c>
       <c r="G13">
-        <f>--(INDEX(NORMATIVOS!$C$108:$AF$108,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$109:$AF$109,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$110:$AF$110,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$111:$AF$111,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$112:$AF$112,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$113:$AF$113,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$114:$AF$114,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$115:$AF$115,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$116:$AF$116,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$117:$AF$117,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$118:$AF$118,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$119:$AF$119,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$120:$AF$120,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$121:$AF$121,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$122:$AF$122,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")</f>
+        <f>--(INDEX(NORMATIVOS!$C$108:$XFD$108,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$109:$XFD$109,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$110:$XFD$110,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$111:$XFD$111,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$112:$XFD$112,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$113:$XFD$113,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$114:$XFD$114,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$115:$XFD$115,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$116:$XFD$116,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$117:$XFD$117,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$118:$XFD$118,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$119:$XFD$119,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$120:$XFD$120,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$121:$XFD$121,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$122:$XFD$122,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")</f>
         <v>4</v>
       </c>
       <c r="H13" s="13">
@@ -32024,15 +32024,15 @@
         <v>150</v>
       </c>
       <c r="E14">
-        <f>--(INDEX(NORMATIVOS!$C$123:$AF$123,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$124:$AF$124,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$125:$AF$125,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$126:$AF$126,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$127:$AF$127,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$128:$AF$128,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$129:$AF$129,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$130:$AF$130,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$131:$AF$131,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$132:$AF$132,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$133:$AF$133,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$134:$AF$134,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$135:$AF$135,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$136:$AF$136,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$137:$AF$137,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$138:$AF$138,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$139:$AF$139,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$140:$AF$140,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$141:$AF$141,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$142:$AF$142,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")</f>
+        <f>--(INDEX(NORMATIVOS!$C$123:$XFD$123,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$124:$XFD$124,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$125:$XFD$125,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$126:$XFD$126,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$127:$XFD$127,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$128:$XFD$128,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$129:$XFD$129,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$130:$XFD$130,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$131:$XFD$131,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$132:$XFD$132,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$133:$XFD$133,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$134:$XFD$134,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$135:$XFD$135,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$136:$XFD$136,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$137:$XFD$137,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$138:$XFD$138,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$139:$XFD$139,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$140:$XFD$140,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$141:$XFD$141,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$142:$XFD$142,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")</f>
         <v>9</v>
       </c>
       <c r="F14">
-        <f>--(INDEX(NORMATIVOS!$C$123:$AF$123,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$124:$AF$124,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$125:$AF$125,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$126:$AF$126,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$127:$AF$127,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$128:$AF$128,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$129:$AF$129,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$130:$AF$130,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$131:$AF$131,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$132:$AF$132,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$133:$AF$133,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$134:$AF$134,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$135:$AF$135,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$136:$AF$136,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$137:$AF$137,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$138:$AF$138,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$139:$AF$139,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$140:$AF$140,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$141:$AF$141,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$142:$AF$142,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")</f>
+        <f>--(INDEX(NORMATIVOS!$C$123:$XFD$123,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$124:$XFD$124,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$125:$XFD$125,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$126:$XFD$126,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$127:$XFD$127,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$128:$XFD$128,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$129:$XFD$129,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$130:$XFD$130,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$131:$XFD$131,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$132:$XFD$132,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$133:$XFD$133,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$134:$XFD$134,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$135:$XFD$135,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$136:$XFD$136,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$137:$XFD$137,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$138:$XFD$138,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$139:$XFD$139,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$140:$XFD$140,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$141:$XFD$141,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$142:$XFD$142,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")</f>
         <v>5</v>
       </c>
       <c r="G14">
-        <f>--(INDEX(NORMATIVOS!$C$123:$AF$123,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$124:$AF$124,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$125:$AF$125,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$126:$AF$126,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$127:$AF$127,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$128:$AF$128,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$129:$AF$129,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$130:$AF$130,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$131:$AF$131,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$132:$AF$132,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$133:$AF$133,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$134:$AF$134,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$135:$AF$135,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$136:$AF$136,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$137:$AF$137,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$138:$AF$138,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$139:$AF$139,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$140:$AF$140,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$141:$AF$141,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$142:$AF$142,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")</f>
+        <f>--(INDEX(NORMATIVOS!$C$123:$XFD$123,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$124:$XFD$124,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$125:$XFD$125,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$126:$XFD$126,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$127:$XFD$127,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$128:$XFD$128,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$129:$XFD$129,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$130:$XFD$130,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$131:$XFD$131,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$132:$XFD$132,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$133:$XFD$133,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$134:$XFD$134,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$135:$XFD$135,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$136:$XFD$136,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$137:$XFD$137,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$138:$XFD$138,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$139:$XFD$139,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$140:$XFD$140,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$141:$XFD$141,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$142:$XFD$142,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")</f>
         <v>6</v>
       </c>
       <c r="H14" s="13">
@@ -32045,15 +32045,15 @@
         <v>172</v>
       </c>
       <c r="E15">
-        <f>--(INDEX(NORMATIVOS!$C$145:$AF$145,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$146:$AF$146,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$147:$AF$147,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$148:$AF$148,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$149:$AF$149,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$150:$AF$150,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$151:$AF$151,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")</f>
+        <f>--(INDEX(NORMATIVOS!$C$145:$XFD$145,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$146:$XFD$146,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$147:$XFD$147,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$148:$XFD$148,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$149:$XFD$149,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$150:$XFD$150,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$151:$XFD$151,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")</f>
         <v>7</v>
       </c>
       <c r="F15">
-        <f>--(INDEX(NORMATIVOS!$C$145:$AF$145,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$146:$AF$146,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$147:$AF$147,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$148:$AF$148,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$149:$AF$149,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$150:$AF$150,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$151:$AF$151,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")</f>
+        <f>--(INDEX(NORMATIVOS!$C$145:$XFD$145,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$146:$XFD$146,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$147:$XFD$147,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$148:$XFD$148,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$149:$XFD$149,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$150:$XFD$150,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$151:$XFD$151,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")</f>
         <v>0</v>
       </c>
       <c r="G15">
-        <f>--(INDEX(NORMATIVOS!$C$145:$AF$145,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$146:$AF$146,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$147:$AF$147,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$148:$AF$148,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$149:$AF$149,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$150:$AF$150,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$151:$AF$151,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")</f>
+        <f>--(INDEX(NORMATIVOS!$C$145:$XFD$145,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$146:$XFD$146,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$147:$XFD$147,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$148:$XFD$148,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$149:$XFD$149,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$150:$XFD$150,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$151:$XFD$151,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")</f>
         <v>0</v>
       </c>
       <c r="H15" s="13">
@@ -32066,15 +32066,15 @@
         <v>180</v>
       </c>
       <c r="E16">
-        <f>--(INDEX(NORMATIVOS!$C$152:$AF$152,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$153:$AF$153,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$154:$AF$154,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$155:$AF$155,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$156:$AF$156,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$157:$AF$157,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$158:$AF$158,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$159:$AF$159,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$160:$AF$160,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$161:$AF$161,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$162:$AF$162,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$163:$AF$163,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$164:$AF$164,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$165:$AF$165,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$166:$AF$166,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$167:$AF$167,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$168:$AF$168,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$169:$AF$169,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$170:$AF$170,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$171:$AF$171,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$172:$AF$172,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$173:$AF$173,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")</f>
+        <f>--(INDEX(NORMATIVOS!$C$152:$XFD$152,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$153:$XFD$153,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$154:$XFD$154,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$155:$XFD$155,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$156:$XFD$156,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$157:$XFD$157,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$158:$XFD$158,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$159:$XFD$159,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$160:$XFD$160,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$161:$XFD$161,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$162:$XFD$162,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$163:$XFD$163,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$164:$XFD$164,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$165:$XFD$165,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$166:$XFD$166,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$167:$XFD$167,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$168:$XFD$168,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$169:$XFD$169,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$170:$XFD$170,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$171:$XFD$171,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$172:$XFD$172,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$173:$XFD$173,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")</f>
         <v>4</v>
       </c>
       <c r="F16">
-        <f>--(INDEX(NORMATIVOS!$C$152:$AF$152,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$153:$AF$153,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$154:$AF$154,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$155:$AF$155,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$156:$AF$156,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$157:$AF$157,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$158:$AF$158,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$159:$AF$159,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$160:$AF$160,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$161:$AF$161,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$162:$AF$162,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$163:$AF$163,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$164:$AF$164,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$165:$AF$165,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$166:$AF$166,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$167:$AF$167,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$168:$AF$168,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$169:$AF$169,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$170:$AF$170,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$171:$AF$171,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$172:$AF$172,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$173:$AF$173,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")</f>
+        <f>--(INDEX(NORMATIVOS!$C$152:$XFD$152,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$153:$XFD$153,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$154:$XFD$154,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$155:$XFD$155,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$156:$XFD$156,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$157:$XFD$157,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$158:$XFD$158,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$159:$XFD$159,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$160:$XFD$160,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$161:$XFD$161,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$162:$XFD$162,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$163:$XFD$163,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$164:$XFD$164,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$165:$XFD$165,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$166:$XFD$166,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$167:$XFD$167,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$168:$XFD$168,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$169:$XFD$169,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$170:$XFD$170,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$171:$XFD$171,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$172:$XFD$172,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$173:$XFD$173,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")</f>
         <v>3</v>
       </c>
       <c r="G16">
-        <f>--(INDEX(NORMATIVOS!$C$152:$AF$152,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$153:$AF$153,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$154:$AF$154,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$155:$AF$155,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$156:$AF$156,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$157:$AF$157,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$158:$AF$158,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$159:$AF$159,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$160:$AF$160,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$161:$AF$161,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$162:$AF$162,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$163:$AF$163,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$164:$AF$164,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$165:$AF$165,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$166:$AF$166,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$167:$AF$167,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$168:$AF$168,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$169:$AF$169,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$170:$AF$170,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$171:$AF$171,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$172:$AF$172,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$173:$AF$173,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")</f>
+        <f>--(INDEX(NORMATIVOS!$C$152:$XFD$152,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$153:$XFD$153,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$154:$XFD$154,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$155:$XFD$155,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$156:$XFD$156,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$157:$XFD$157,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$158:$XFD$158,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$159:$XFD$159,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$160:$XFD$160,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$161:$XFD$161,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$162:$XFD$162,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$163:$XFD$163,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$164:$XFD$164,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$165:$XFD$165,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$166:$XFD$166,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$167:$XFD$167,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$168:$XFD$168,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$169:$XFD$169,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$170:$XFD$170,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$171:$XFD$171,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$172:$XFD$172,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$173:$XFD$173,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")</f>
         <v>15</v>
       </c>
       <c r="H16" s="13">
@@ -32087,15 +32087,15 @@
         <v>308</v>
       </c>
       <c r="E17">
-        <f>--(INDEX(NORMATIVOS!$C$176:$AF$176,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$177:$AF$177,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$178:$AF$178,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$179:$AF$179,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$180:$AF$180,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$181:$AF$181,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$182:$AF$182,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$183:$AF$183,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$184:$AF$184,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$185:$AF$185,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$186:$AF$186,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$187:$AF$187,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$188:$AF$188,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$189:$AF$189,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$190:$AF$190,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$191:$AF$191,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$192:$AF$192,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$193:$AF$193,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")</f>
+        <f>--(INDEX(NORMATIVOS!$C$176:$XFD$176,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$177:$XFD$177,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$178:$XFD$178,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$179:$XFD$179,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$180:$XFD$180,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$181:$XFD$181,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$182:$XFD$182,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$183:$XFD$183,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$184:$XFD$184,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$185:$XFD$185,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$186:$XFD$186,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$187:$XFD$187,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$188:$XFD$188,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$189:$XFD$189,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$190:$XFD$190,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$191:$XFD$191,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$192:$XFD$192,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$193:$XFD$193,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")</f>
         <v>7</v>
       </c>
       <c r="F17">
-        <f>--(INDEX(NORMATIVOS!$C$176:$AF$176,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$177:$AF$177,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$178:$AF$178,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$179:$AF$179,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$180:$AF$180,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$181:$AF$181,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$182:$AF$182,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$183:$AF$183,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$184:$AF$184,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$185:$AF$185,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$186:$AF$186,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$187:$AF$187,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$188:$AF$188,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$189:$AF$189,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$190:$AF$190,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$191:$AF$191,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$192:$AF$192,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$193:$AF$193,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")</f>
+        <f>--(INDEX(NORMATIVOS!$C$176:$XFD$176,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$177:$XFD$177,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$178:$XFD$178,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$179:$XFD$179,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$180:$XFD$180,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$181:$XFD$181,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$182:$XFD$182,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$183:$XFD$183,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$184:$XFD$184,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$185:$XFD$185,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$186:$XFD$186,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$187:$XFD$187,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$188:$XFD$188,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$189:$XFD$189,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$190:$XFD$190,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$191:$XFD$191,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$192:$XFD$192,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$193:$XFD$193,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")</f>
         <v>2</v>
       </c>
       <c r="G17">
-        <f>--(INDEX(NORMATIVOS!$C$176:$AF$176,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$177:$AF$177,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$178:$AF$178,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$179:$AF$179,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$180:$AF$180,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$181:$AF$181,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$182:$AF$182,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$183:$AF$183,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$184:$AF$184,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$185:$AF$185,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$186:$AF$186,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$187:$AF$187,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$188:$AF$188,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$189:$AF$189,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$190:$AF$190,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$191:$AF$191,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$192:$AF$192,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$193:$AF$193,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")</f>
+        <f>--(INDEX(NORMATIVOS!$C$176:$XFD$176,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$177:$XFD$177,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$178:$XFD$178,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$179:$XFD$179,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$180:$XFD$180,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$181:$XFD$181,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$182:$XFD$182,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$183:$XFD$183,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$184:$XFD$184,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$185:$XFD$185,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$186:$XFD$186,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$187:$XFD$187,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$188:$XFD$188,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$189:$XFD$189,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$190:$XFD$190,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$191:$XFD$191,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$192:$XFD$192,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$193:$XFD$193,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")</f>
         <v>6</v>
       </c>
       <c r="H17" s="13">
@@ -32108,15 +32108,15 @@
         <v>220</v>
       </c>
       <c r="E18">
-        <f>--(INDEX(NORMATIVOS!$C$194:$AF$194,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$195:$AF$195,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$196:$AF$196,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$197:$AF$197,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$198:$AF$198,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$199:$AF$199,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$200:$AF$200,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$201:$AF$201,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$202:$AF$202,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$203:$AF$203,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$204:$AF$204,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$205:$AF$205,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$206:$AF$206,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$207:$AF$207,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$209:$AF$209,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$210:$AF$210,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$211:$AF$211,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$212:$AF$212,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$213:$AF$213,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$214:$AF$214,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$215:$AF$215,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$216:$AF$216,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$217:$AF$217,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$218:$AF$218,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")</f>
+        <f>--(INDEX(NORMATIVOS!$C$194:$XFD$194,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$195:$XFD$195,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$196:$XFD$196,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$197:$XFD$197,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$198:$XFD$198,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$199:$XFD$199,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$200:$XFD$200,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$201:$XFD$201,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$202:$XFD$202,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$203:$XFD$203,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$204:$XFD$204,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$205:$XFD$205,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$206:$XFD$206,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$207:$XFD$207,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$209:$XFD$209,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$210:$XFD$210,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$211:$XFD$211,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$212:$XFD$212,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$213:$XFD$213,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$214:$XFD$214,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$215:$XFD$215,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$216:$XFD$216,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$217:$XFD$217,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$218:$XFD$218,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")</f>
         <v>12</v>
       </c>
       <c r="F18">
-        <f>--(INDEX(NORMATIVOS!$C$194:$AF$194,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$195:$AF$195,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$196:$AF$196,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$197:$AF$197,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$198:$AF$198,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$199:$AF$199,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$200:$AF$200,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$201:$AF$201,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$202:$AF$202,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$203:$AF$203,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$204:$AF$204,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$205:$AF$205,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$206:$AF$206,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$207:$AF$207,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$209:$AF$209,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$210:$AF$210,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$211:$AF$211,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$212:$AF$212,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$213:$AF$213,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$214:$AF$214,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$215:$AF$215,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$216:$AF$216,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$217:$AF$217,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$218:$AF$218,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")</f>
+        <f>--(INDEX(NORMATIVOS!$C$194:$XFD$194,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$195:$XFD$195,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$196:$XFD$196,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$197:$XFD$197,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$198:$XFD$198,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$199:$XFD$199,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$200:$XFD$200,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$201:$XFD$201,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$202:$XFD$202,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$203:$XFD$203,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$204:$XFD$204,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$205:$XFD$205,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$206:$XFD$206,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$207:$XFD$207,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$209:$XFD$209,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$210:$XFD$210,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$211:$XFD$211,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$212:$XFD$212,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$213:$XFD$213,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$214:$XFD$214,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$215:$XFD$215,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$216:$XFD$216,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$217:$XFD$217,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$218:$XFD$218,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")</f>
         <v>3</v>
       </c>
       <c r="G18">
-        <f>--(INDEX(NORMATIVOS!$C$194:$AF$194,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$195:$AF$195,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$196:$AF$196,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$197:$AF$197,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$198:$AF$198,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$199:$AF$199,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$200:$AF$200,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$201:$AF$201,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$202:$AF$202,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$203:$AF$203,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$204:$AF$204,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$205:$AF$205,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$206:$AF$206,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$207:$AF$207,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$209:$AF$209,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$210:$AF$210,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$211:$AF$211,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$212:$AF$212,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$213:$AF$213,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$214:$AF$214,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$215:$AF$215,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$216:$AF$216,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$217:$AF$217,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$218:$AF$218,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")</f>
+        <f>--(INDEX(NORMATIVOS!$C$194:$XFD$194,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$195:$XFD$195,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$196:$XFD$196,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$197:$XFD$197,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$198:$XFD$198,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$199:$XFD$199,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$200:$XFD$200,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$201:$XFD$201,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$202:$XFD$202,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$203:$XFD$203,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$204:$XFD$204,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$205:$XFD$205,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$206:$XFD$206,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$207:$XFD$207,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$209:$XFD$209,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$210:$XFD$210,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$211:$XFD$211,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$212:$XFD$212,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$213:$XFD$213,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$214:$XFD$214,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$215:$XFD$215,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$216:$XFD$216,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$217:$XFD$217,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$218:$XFD$218,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")</f>
         <v>8</v>
       </c>
       <c r="H18" s="13">
@@ -32129,15 +32129,15 @@
         <v>242</v>
       </c>
       <c r="E19">
-        <f>--(INDEX(NORMATIVOS!$C$219:$AF$219,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$220:$AF$220,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$221:$AF$221,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$222:$AF$222,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$223:$AF$223,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$224:$AF$224,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$225:$AF$225,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$226:$AF$226,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$227:$AF$227,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$228:$AF$228,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$229:$AF$229,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$230:$AF$230,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$231:$AF$231,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")</f>
+        <f>--(INDEX(NORMATIVOS!$C$219:$XFD$219,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$220:$XFD$220,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$221:$XFD$221,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$222:$XFD$222,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$223:$XFD$223,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$224:$XFD$224,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$225:$XFD$225,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$226:$XFD$226,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$227:$XFD$227,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$228:$XFD$228,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$229:$XFD$229,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$230:$XFD$230,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$231:$XFD$231,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")</f>
         <v>6</v>
       </c>
       <c r="F19">
-        <f>--(INDEX(NORMATIVOS!$C$219:$AF$219,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$220:$AF$220,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$221:$AF$221,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$222:$AF$222,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$223:$AF$223,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$224:$AF$224,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$225:$AF$225,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$226:$AF$226,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$227:$AF$227,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$228:$AF$228,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$229:$AF$229,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$230:$AF$230,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$231:$AF$231,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")</f>
+        <f>--(INDEX(NORMATIVOS!$C$219:$XFD$219,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$220:$XFD$220,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$221:$XFD$221,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$222:$XFD$222,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$223:$XFD$223,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$224:$XFD$224,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$225:$XFD$225,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$226:$XFD$226,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$227:$XFD$227,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$228:$XFD$228,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$229:$XFD$229,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$230:$XFD$230,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$231:$XFD$231,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")</f>
         <v>2</v>
       </c>
       <c r="G19">
-        <f>--(INDEX(NORMATIVOS!$C$219:$AF$219,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$220:$AF$220,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$221:$AF$221,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$222:$AF$222,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$223:$AF$223,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$224:$AF$224,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$225:$AF$225,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$226:$AF$226,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$227:$AF$227,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$228:$AF$228,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$229:$AF$229,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$230:$AF$230,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$231:$AF$231,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")</f>
+        <f>--(INDEX(NORMATIVOS!$C$219:$XFD$219,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$220:$XFD$220,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$221:$XFD$221,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$222:$XFD$222,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$223:$XFD$223,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$224:$XFD$224,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$225:$XFD$225,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$226:$XFD$226,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$227:$XFD$227,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$228:$XFD$228,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$229:$XFD$229,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$230:$XFD$230,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$231:$XFD$231,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")</f>
         <v>5</v>
       </c>
       <c r="H19" s="13">
@@ -32150,15 +32150,15 @@
         <v>253</v>
       </c>
       <c r="E20">
-        <f>--(INDEX(NORMATIVOS!$C$234:$AF$234,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$235:$AF$235,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$236:$AF$236,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$237:$AF$237,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$238:$AF$238,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$239:$AF$239,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$240:$AF$240,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$241:$AF$241,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$242:$AF$242,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$243:$AF$243,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$244:$AF$244,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$245:$AF$245,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$246:$AF$246,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$247:$AF$247,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$248:$AF$248,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$249:$AF$249,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$250:$AF$250,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$251:$AF$251,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$252:$AF$252,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$253:$AF$253,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$254:$AF$254,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$255:$AF$255,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$256:$AF$256,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$257:$AF$257,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$258:$AF$258,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$259:$AF$259,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$260:$AF$260,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$261:$AF$261,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")</f>
+        <f>--(INDEX(NORMATIVOS!$C$234:$XFD$234,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$235:$XFD$235,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$236:$XFD$236,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$237:$XFD$237,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$238:$XFD$238,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$239:$XFD$239,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$240:$XFD$240,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$241:$XFD$241,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$242:$XFD$242,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$243:$XFD$243,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$244:$XFD$244,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$245:$XFD$245,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$246:$XFD$246,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$247:$XFD$247,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$248:$XFD$248,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$249:$XFD$249,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$250:$XFD$250,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$251:$XFD$251,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$252:$XFD$252,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$253:$XFD$253,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$254:$XFD$254,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$255:$XFD$255,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$256:$XFD$256,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$257:$XFD$257,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$258:$XFD$258,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$259:$XFD$259,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$260:$XFD$260,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$261:$XFD$261,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")</f>
         <v>13</v>
       </c>
       <c r="F20">
-        <f>--(INDEX(NORMATIVOS!$C$234:$AF$234,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$235:$AF$235,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$236:$AF$236,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$237:$AF$237,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$238:$AF$238,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$239:$AF$239,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$240:$AF$240,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$241:$AF$241,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$242:$AF$242,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$243:$AF$243,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$244:$AF$244,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$245:$AF$245,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$246:$AF$246,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$247:$AF$247,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$248:$AF$248,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$249:$AF$249,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$250:$AF$250,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$251:$AF$251,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$252:$AF$252,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$253:$AF$253,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$254:$AF$254,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$255:$AF$255,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$256:$AF$256,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$257:$AF$257,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$258:$AF$258,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$259:$AF$259,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$260:$AF$260,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$261:$AF$261,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")</f>
+        <f>--(INDEX(NORMATIVOS!$C$234:$XFD$234,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$235:$XFD$235,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$236:$XFD$236,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$237:$XFD$237,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$238:$XFD$238,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$239:$XFD$239,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$240:$XFD$240,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$241:$XFD$241,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$242:$XFD$242,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$243:$XFD$243,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$244:$XFD$244,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$245:$XFD$245,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$246:$XFD$246,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$247:$XFD$247,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$248:$XFD$248,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$249:$XFD$249,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$250:$XFD$250,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$251:$XFD$251,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$252:$XFD$252,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$253:$XFD$253,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$254:$XFD$254,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$255:$XFD$255,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$256:$XFD$256,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$257:$XFD$257,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$258:$XFD$258,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$259:$XFD$259,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$260:$XFD$260,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$261:$XFD$261,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")</f>
         <v>4</v>
       </c>
       <c r="G20">
-        <f>--(INDEX(NORMATIVOS!$C$234:$AF$234,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$235:$AF$235,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$236:$AF$236,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$237:$AF$237,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$238:$AF$238,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$239:$AF$239,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$240:$AF$240,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$241:$AF$241,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$242:$AF$242,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$243:$AF$243,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$244:$AF$244,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$245:$AF$245,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$246:$AF$246,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$247:$AF$247,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$248:$AF$248,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$249:$AF$249,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$250:$AF$250,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$251:$AF$251,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$252:$AF$252,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$253:$AF$253,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$254:$AF$254,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$255:$AF$255,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$256:$AF$256,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$257:$AF$257,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$258:$AF$258,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$259:$AF$259,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$260:$AF$260,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$261:$AF$261,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")</f>
+        <f>--(INDEX(NORMATIVOS!$C$234:$XFD$234,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$235:$XFD$235,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$236:$XFD$236,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$237:$XFD$237,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$238:$XFD$238,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$239:$XFD$239,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$240:$XFD$240,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$241:$XFD$241,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$242:$XFD$242,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$243:$XFD$243,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$244:$XFD$244,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$245:$XFD$245,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$246:$XFD$246,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$247:$XFD$247,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$248:$XFD$248,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$249:$XFD$249,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$250:$XFD$250,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$251:$XFD$251,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$252:$XFD$252,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$253:$XFD$253,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$254:$XFD$254,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$255:$XFD$255,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$256:$XFD$256,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$257:$XFD$257,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$258:$XFD$258,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$259:$XFD$259,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$260:$XFD$260,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$261:$XFD$261,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")</f>
         <v>11</v>
       </c>
       <c r="H20" s="13">
@@ -32171,15 +32171,15 @@
         <v>278</v>
       </c>
       <c r="E21">
-        <f>--(INDEX(NORMATIVOS!$C$262:$AF$262,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$263:$AF$263,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$264:$AF$264,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$266:$AF$266,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$267:$AF$267,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$268:$AF$268,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$269:$AF$269,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$270:$AF$270,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$271:$AF$271,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$272:$AF$272,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$273:$AF$273,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$274:$AF$274,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$275:$AF$275,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$276:$AF$276,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$277:$AF$277,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$278:$AF$278,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$279:$AF$279,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Consolidado")</f>
+        <f>--(INDEX(NORMATIVOS!$C$262:$XFD$262,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$263:$XFD$263,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$264:$XFD$264,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$266:$XFD$266,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$267:$XFD$267,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$268:$XFD$268,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$269:$XFD$269,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$270:$XFD$270,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$271:$XFD$271,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$272:$XFD$272,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$273:$XFD$273,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$274:$XFD$274,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$275:$XFD$275,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$276:$XFD$276,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$277:$XFD$277,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$278:$XFD$278,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")+--(INDEX(NORMATIVOS!$C$279:$XFD$279,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Consolidado")</f>
         <v>7</v>
       </c>
       <c r="F21">
-        <f>--(INDEX(NORMATIVOS!$C$262:$AF$262,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$263:$AF$263,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$264:$AF$264,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$266:$AF$266,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$267:$AF$267,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$268:$AF$268,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$269:$AF$269,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$270:$AF$270,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$271:$AF$271,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$272:$AF$272,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$273:$AF$273,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$274:$AF$274,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$275:$AF$275,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$276:$AF$276,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$277:$AF$277,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$278:$AF$278,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$279:$AF$279,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="En proceso")</f>
+        <f>--(INDEX(NORMATIVOS!$C$262:$XFD$262,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$263:$XFD$263,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$264:$XFD$264,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$266:$XFD$266,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$267:$XFD$267,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$268:$XFD$268,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$269:$XFD$269,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$270:$XFD$270,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$271:$XFD$271,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$272:$XFD$272,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$273:$XFD$273,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$274:$XFD$274,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$275:$XFD$275,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$276:$XFD$276,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$277:$XFD$277,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$278:$XFD$278,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")+--(INDEX(NORMATIVOS!$C$279:$XFD$279,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="En proceso")</f>
         <v>3</v>
       </c>
       <c r="G21">
-        <f>--(INDEX(NORMATIVOS!$C$262:$AF$262,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$263:$AF$263,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$264:$AF$264,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$266:$AF$266,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$267:$AF$267,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$268:$AF$268,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$269:$AF$269,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$270:$AF$270,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$271:$AF$271,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$272:$AF$272,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$273:$AF$273,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$274:$AF$274,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$275:$AF$275,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$276:$AF$276,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$277:$AF$277,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$278:$AF$278,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$279:$AF$279,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))="Proyección")</f>
+        <f>--(INDEX(NORMATIVOS!$C$262:$XFD$262,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$263:$XFD$263,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$264:$XFD$264,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$266:$XFD$266,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$267:$XFD$267,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$268:$XFD$268,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$269:$XFD$269,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$270:$XFD$270,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$271:$XFD$271,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$272:$XFD$272,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$273:$XFD$273,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$274:$XFD$274,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$275:$XFD$275,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$276:$XFD$276,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$277:$XFD$277,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$278:$XFD$278,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")+--(INDEX(NORMATIVOS!$C$279:$XFD$279,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))="Proyección")</f>
         <v>7</v>
       </c>
       <c r="H21" s="13">
@@ -32213,7 +32213,7 @@
         <v>32</v>
       </c>
       <c r="C27" t="str">
-        <f>INDEX(NORMATIVOS!$C$3:$AF$3,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$3:$XFD$3,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32225,7 +32225,7 @@
         <v>35</v>
       </c>
       <c r="C28" t="str">
-        <f>INDEX(NORMATIVOS!$C$4:$AF$4,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$4:$XFD$4,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32237,7 +32237,7 @@
         <v>36</v>
       </c>
       <c r="C29" t="str">
-        <f>INDEX(NORMATIVOS!$C$5:$AF$5,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$5:$XFD$5,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32249,7 +32249,7 @@
         <v>37</v>
       </c>
       <c r="C30" t="str">
-        <f>INDEX(NORMATIVOS!$C$6:$AF$6,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$6:$XFD$6,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32261,7 +32261,7 @@
         <v>38</v>
       </c>
       <c r="C31" t="str">
-        <f>INDEX(NORMATIVOS!$C$7:$AF$7,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$7:$XFD$7,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32273,7 +32273,7 @@
         <v>39</v>
       </c>
       <c r="C32" t="str">
-        <f>INDEX(NORMATIVOS!$C$8:$AF$8,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$8:$XFD$8,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32285,7 +32285,7 @@
         <v>40</v>
       </c>
       <c r="C33" t="str">
-        <f>INDEX(NORMATIVOS!$C$9:$AF$9,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$9:$XFD$9,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32297,7 +32297,7 @@
         <v>41</v>
       </c>
       <c r="C34" t="str">
-        <f>INDEX(NORMATIVOS!$C$10:$AF$10,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$10:$XFD$10,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32309,7 +32309,7 @@
         <v>42</v>
       </c>
       <c r="C35" t="str">
-        <f>INDEX(NORMATIVOS!$C$11:$AF$11,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$11:$XFD$11,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32321,7 +32321,7 @@
         <v>43</v>
       </c>
       <c r="C36" t="str">
-        <f>INDEX(NORMATIVOS!$C$12:$AF$12,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$12:$XFD$12,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32333,7 +32333,7 @@
         <v>44</v>
       </c>
       <c r="C37" t="str">
-        <f>INDEX(NORMATIVOS!$C$13:$AF$13,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$13:$XFD$13,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32345,7 +32345,7 @@
         <v>45</v>
       </c>
       <c r="C38" t="str">
-        <f>INDEX(NORMATIVOS!$C$14:$AF$14,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$14:$XFD$14,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32357,7 +32357,7 @@
         <v>46</v>
       </c>
       <c r="C39" t="str">
-        <f>INDEX(NORMATIVOS!$C$15:$AF$15,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$15:$XFD$15,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32369,7 +32369,7 @@
         <v>47</v>
       </c>
       <c r="C40" t="str">
-        <f>INDEX(NORMATIVOS!$C$16:$AF$16,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$16:$XFD$16,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -32381,7 +32381,7 @@
         <v>322</v>
       </c>
       <c r="C41" t="str">
-        <f>INDEX(NORMATIVOS!$C$17:$AF$17,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$17:$XFD$17,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32393,7 +32393,7 @@
         <v>50</v>
       </c>
       <c r="C42" t="str">
-        <f>INDEX(NORMATIVOS!$C$18:$AF$18,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$18:$XFD$18,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32405,7 +32405,7 @@
         <v>51</v>
       </c>
       <c r="C43" t="str">
-        <f>INDEX(NORMATIVOS!$C$19:$AF$19,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$19:$XFD$19,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32417,7 +32417,7 @@
         <v>52</v>
       </c>
       <c r="C44" t="str">
-        <f>INDEX(NORMATIVOS!$C$20:$AF$20,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$20:$XFD$20,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32429,7 +32429,7 @@
         <v>53</v>
       </c>
       <c r="C45" t="str">
-        <f>INDEX(NORMATIVOS!$C$21:$AF$21,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$21:$XFD$21,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32441,7 +32441,7 @@
         <v>54</v>
       </c>
       <c r="C46" t="str">
-        <f>INDEX(NORMATIVOS!$C$22:$AF$22,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$22:$XFD$22,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32453,7 +32453,7 @@
         <v>323</v>
       </c>
       <c r="C47" t="str">
-        <f>INDEX(NORMATIVOS!$C$23:$AF$23,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$23:$XFD$23,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32465,7 +32465,7 @@
         <v>56</v>
       </c>
       <c r="C48" t="str">
-        <f>INDEX(NORMATIVOS!$C$24:$AF$24,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$24:$XFD$24,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32477,7 +32477,7 @@
         <v>57</v>
       </c>
       <c r="C49" t="str">
-        <f>INDEX(NORMATIVOS!$C$25:$AF$25,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$25:$XFD$25,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
         <v>58</v>
       </c>
       <c r="C50" t="str">
-        <f>INDEX(NORMATIVOS!$C$26:$AF$26,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$26:$XFD$26,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -32501,7 +32501,7 @@
         <v>324</v>
       </c>
       <c r="C51" t="str">
-        <f>INDEX(NORMATIVOS!$C$27:$AF$27,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$27:$XFD$27,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -32513,7 +32513,7 @@
         <v>61</v>
       </c>
       <c r="C52" t="str">
-        <f>INDEX(NORMATIVOS!$C$28:$AF$28,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$28:$XFD$28,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32525,7 +32525,7 @@
         <v>62</v>
       </c>
       <c r="C53" t="str">
-        <f>INDEX(NORMATIVOS!$C$29:$AF$29,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$29:$XFD$29,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32537,7 +32537,7 @@
         <v>63</v>
       </c>
       <c r="C54" t="str">
-        <f>INDEX(NORMATIVOS!$C$30:$AF$30,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$30:$XFD$30,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32549,7 +32549,7 @@
         <v>64</v>
       </c>
       <c r="C55" t="str">
-        <f>INDEX(NORMATIVOS!$C$31:$AF$31,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$31:$XFD$31,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32561,7 +32561,7 @@
         <v>65</v>
       </c>
       <c r="C56" t="str">
-        <f>INDEX(NORMATIVOS!$C$32:$AF$32,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$32:$XFD$32,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32573,7 +32573,7 @@
         <v>66</v>
       </c>
       <c r="C57" t="str">
-        <f>INDEX(NORMATIVOS!$C$33:$AF$33,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$33:$XFD$33,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32585,7 +32585,7 @@
         <v>67</v>
       </c>
       <c r="C58" t="str">
-        <f>INDEX(NORMATIVOS!$C$34:$AF$34,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$34:$XFD$34,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32597,7 +32597,7 @@
         <v>68</v>
       </c>
       <c r="C59" t="str">
-        <f>INDEX(NORMATIVOS!$C$35:$AF$35,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$35:$XFD$35,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32609,7 +32609,7 @@
         <v>69</v>
       </c>
       <c r="C60" t="str">
-        <f>INDEX(NORMATIVOS!$C$36:$AF$36,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$36:$XFD$36,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>N/A</v>
       </c>
     </row>
@@ -32621,7 +32621,7 @@
         <v>70</v>
       </c>
       <c r="C61" t="str">
-        <f>INDEX(NORMATIVOS!$C$37:$AF$37,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$37:$XFD$37,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -32633,7 +32633,7 @@
         <v>72</v>
       </c>
       <c r="C62" t="str">
-        <f>INDEX(NORMATIVOS!$C$38:$AF$38,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$38:$XFD$38,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32645,7 +32645,7 @@
         <v>73</v>
       </c>
       <c r="C63" t="str">
-        <f>INDEX(NORMATIVOS!$C$39:$AF$39,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$39:$XFD$39,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32657,7 +32657,7 @@
         <v>74</v>
       </c>
       <c r="C64" t="str">
-        <f>INDEX(NORMATIVOS!$C$40:$AF$40,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$40:$XFD$40,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32669,7 +32669,7 @@
         <v>75</v>
       </c>
       <c r="C65" t="str">
-        <f>INDEX(NORMATIVOS!$C$41:$AF$41,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$41:$XFD$41,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32681,7 +32681,7 @@
         <v>76</v>
       </c>
       <c r="C66" t="str">
-        <f>INDEX(NORMATIVOS!$C$42:$AF$42,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$42:$XFD$42,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -32693,7 +32693,7 @@
         <v>77</v>
       </c>
       <c r="C67" t="str">
-        <f>INDEX(NORMATIVOS!$C$43:$AF$43,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$43:$XFD$43,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -32705,7 +32705,7 @@
         <v>78</v>
       </c>
       <c r="C68" t="str">
-        <f>INDEX(NORMATIVOS!$C$44:$AF$44,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$44:$XFD$44,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -32717,7 +32717,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="str">
-        <f>INDEX(NORMATIVOS!$C$45:$AF$45,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$45:$XFD$45,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -32729,7 +32729,7 @@
         <v>80</v>
       </c>
       <c r="C70" t="str">
-        <f>INDEX(NORMATIVOS!$C$46:$AF$46,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$46:$XFD$46,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -32741,7 +32741,7 @@
         <v>83</v>
       </c>
       <c r="C71" t="str">
-        <f>INDEX(NORMATIVOS!$C$49:$AF$49,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$49:$XFD$49,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32753,7 +32753,7 @@
         <v>84</v>
       </c>
       <c r="C72" t="str">
-        <f>INDEX(NORMATIVOS!$C$50:$AF$50,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$50:$XFD$50,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32765,7 +32765,7 @@
         <v>85</v>
       </c>
       <c r="C73" t="str">
-        <f>INDEX(NORMATIVOS!$C$51:$AF$51,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$51:$XFD$51,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
         <v>86</v>
       </c>
       <c r="C74" t="str">
-        <f>INDEX(NORMATIVOS!$C$52:$AF$52,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$52:$XFD$52,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32789,7 +32789,7 @@
         <v>87</v>
       </c>
       <c r="C75" t="str">
-        <f>INDEX(NORMATIVOS!$C$53:$AF$53,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$53:$XFD$53,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32801,7 +32801,7 @@
         <v>88</v>
       </c>
       <c r="C76" t="str">
-        <f>INDEX(NORMATIVOS!$C$54:$AF$54,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$54:$XFD$54,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32813,7 +32813,7 @@
         <v>89</v>
       </c>
       <c r="C77" t="str">
-        <f>INDEX(NORMATIVOS!$C$55:$AF$55,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$55:$XFD$55,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32825,7 +32825,7 @@
         <v>90</v>
       </c>
       <c r="C78" t="str">
-        <f>INDEX(NORMATIVOS!$C$56:$AF$56,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$56:$XFD$56,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32837,7 +32837,7 @@
         <v>91</v>
       </c>
       <c r="C79" t="str">
-        <f>INDEX(NORMATIVOS!$C$57:$AF$57,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$57:$XFD$57,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32849,7 +32849,7 @@
         <v>92</v>
       </c>
       <c r="C80" t="str">
-        <f>INDEX(NORMATIVOS!$C$58:$AF$58,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$58:$XFD$58,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32861,7 +32861,7 @@
         <v>93</v>
       </c>
       <c r="C81" t="str">
-        <f>INDEX(NORMATIVOS!$C$59:$AF$59,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$59:$XFD$59,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32873,7 +32873,7 @@
         <v>94</v>
       </c>
       <c r="C82" t="str">
-        <f>INDEX(NORMATIVOS!$C$60:$AF$60,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$60:$XFD$60,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32885,7 +32885,7 @@
         <v>95</v>
       </c>
       <c r="C83" t="str">
-        <f>INDEX(NORMATIVOS!$C$61:$AF$61,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$61:$XFD$61,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32897,7 +32897,7 @@
         <v>325</v>
       </c>
       <c r="C84" t="str">
-        <f>INDEX(NORMATIVOS!$C$62:$AF$62,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$62:$XFD$62,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32909,7 +32909,7 @@
         <v>97</v>
       </c>
       <c r="C85" t="str">
-        <f>INDEX(NORMATIVOS!$C$63:$AF$63,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$63:$XFD$63,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32921,7 +32921,7 @@
         <v>98</v>
       </c>
       <c r="C86" t="str">
-        <f>INDEX(NORMATIVOS!$C$64:$AF$64,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$64:$XFD$64,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32933,7 +32933,7 @@
         <v>100</v>
       </c>
       <c r="C87" t="str">
-        <f>INDEX(NORMATIVOS!$C$65:$AF$65,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$65:$XFD$65,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32945,7 +32945,7 @@
         <v>101</v>
       </c>
       <c r="C88" t="str">
-        <f>INDEX(NORMATIVOS!$C$66:$AF$66,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$66:$XFD$66,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32957,7 +32957,7 @@
         <v>94</v>
       </c>
       <c r="C89" t="str">
-        <f>INDEX(NORMATIVOS!$C$67:$AF$67,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$67:$XFD$67,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32969,7 +32969,7 @@
         <v>102</v>
       </c>
       <c r="C90" t="str">
-        <f>INDEX(NORMATIVOS!$C$68:$AF$68,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$68:$XFD$68,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32981,7 +32981,7 @@
         <v>103</v>
       </c>
       <c r="C91" t="str">
-        <f>INDEX(NORMATIVOS!$C$69:$AF$69,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$69:$XFD$69,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -32993,7 +32993,7 @@
         <v>92</v>
       </c>
       <c r="C92" t="str">
-        <f>INDEX(NORMATIVOS!$C$70:$AF$70,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$70:$XFD$70,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33005,7 +33005,7 @@
         <v>95</v>
       </c>
       <c r="C93" t="str">
-        <f>INDEX(NORMATIVOS!$C$71:$AF$71,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$71:$XFD$71,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33017,7 +33017,7 @@
         <v>325</v>
       </c>
       <c r="C94" t="str">
-        <f>INDEX(NORMATIVOS!$C$72:$AF$72,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$72:$XFD$72,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33029,7 +33029,7 @@
         <v>104</v>
       </c>
       <c r="C95" t="str">
-        <f>INDEX(NORMATIVOS!$C$73:$AF$73,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$73:$XFD$73,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33041,7 +33041,7 @@
         <v>105</v>
       </c>
       <c r="C96" t="str">
-        <f>INDEX(NORMATIVOS!$C$74:$AF$74,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$74:$XFD$74,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33053,7 +33053,7 @@
         <v>98</v>
       </c>
       <c r="C97" t="str">
-        <f>INDEX(NORMATIVOS!$C$75:$AF$75,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$75:$XFD$75,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>N/A</v>
       </c>
     </row>
@@ -33065,7 +33065,7 @@
         <v>106</v>
       </c>
       <c r="C98" t="str">
-        <f>INDEX(NORMATIVOS!$C$76:$AF$76,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$76:$XFD$76,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>N/A</v>
       </c>
     </row>
@@ -33077,7 +33077,7 @@
         <v>107</v>
       </c>
       <c r="C99" t="str">
-        <f>INDEX(NORMATIVOS!$C$77:$AF$77,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$77:$XFD$77,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>N/A</v>
       </c>
     </row>
@@ -33089,7 +33089,7 @@
         <v>108</v>
       </c>
       <c r="C100" t="str">
-        <f>INDEX(NORMATIVOS!$C$78:$AF$78,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$78:$XFD$78,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>N/A</v>
       </c>
     </row>
@@ -33101,7 +33101,7 @@
         <v>110</v>
       </c>
       <c r="C101" t="str">
-        <f>INDEX(NORMATIVOS!$C$79:$AF$79,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$79:$XFD$79,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33113,7 +33113,7 @@
         <v>111</v>
       </c>
       <c r="C102" t="str">
-        <f>INDEX(NORMATIVOS!$C$80:$AF$80,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$80:$XFD$80,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33125,7 +33125,7 @@
         <v>112</v>
       </c>
       <c r="C103" t="str">
-        <f>INDEX(NORMATIVOS!$C$81:$AF$81,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$81:$XFD$81,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33137,7 +33137,7 @@
         <v>113</v>
       </c>
       <c r="C104" t="str">
-        <f>INDEX(NORMATIVOS!$C$82:$AF$82,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$82:$XFD$82,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33149,7 +33149,7 @@
         <v>326</v>
       </c>
       <c r="C105" t="str">
-        <f>INDEX(NORMATIVOS!$C$83:$AF$83,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$83:$XFD$83,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33161,7 +33161,7 @@
         <v>115</v>
       </c>
       <c r="C106" t="str">
-        <f>INDEX(NORMATIVOS!$C$84:$AF$84,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$84:$XFD$84,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33173,7 +33173,7 @@
         <v>327</v>
       </c>
       <c r="C107" t="str">
-        <f>INDEX(NORMATIVOS!$C$85:$AF$85,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$85:$XFD$85,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33185,7 +33185,7 @@
         <v>117</v>
       </c>
       <c r="C108" t="str">
-        <f>INDEX(NORMATIVOS!$C$86:$AF$86,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$86:$XFD$86,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -33197,7 +33197,7 @@
         <v>118</v>
       </c>
       <c r="C109" t="str">
-        <f>INDEX(NORMATIVOS!$C$87:$AF$87,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$87:$XFD$87,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33209,7 +33209,7 @@
         <v>119</v>
       </c>
       <c r="C110" t="str">
-        <f>INDEX(NORMATIVOS!$C$88:$AF$88,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$88:$XFD$88,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33221,7 +33221,7 @@
         <v>120</v>
       </c>
       <c r="C111" t="str">
-        <f>INDEX(NORMATIVOS!$C$89:$AF$89,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$89:$XFD$89,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -33233,7 +33233,7 @@
         <v>92</v>
       </c>
       <c r="C112" t="str">
-        <f>INDEX(NORMATIVOS!$C$90:$AF$90,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$90:$XFD$90,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33245,7 +33245,7 @@
         <v>121</v>
       </c>
       <c r="C113" t="str">
-        <f>INDEX(NORMATIVOS!$C$91:$AF$91,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$91:$XFD$91,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -33257,7 +33257,7 @@
         <v>122</v>
       </c>
       <c r="C114" t="str">
-        <f>INDEX(NORMATIVOS!$C$92:$AF$92,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$92:$XFD$92,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33269,7 +33269,7 @@
         <v>123</v>
       </c>
       <c r="C115" t="str">
-        <f>INDEX(NORMATIVOS!$C$93:$AF$93,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$93:$XFD$93,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33281,7 +33281,7 @@
         <v>124</v>
       </c>
       <c r="C116" t="str">
-        <f>INDEX(NORMATIVOS!$C$94:$AF$94,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$94:$XFD$94,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33293,7 +33293,7 @@
         <v>125</v>
       </c>
       <c r="C117" t="str">
-        <f>INDEX(NORMATIVOS!$C$95:$AF$95,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$95:$XFD$95,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33305,7 +33305,7 @@
         <v>107</v>
       </c>
       <c r="C118" t="str">
-        <f>INDEX(NORMATIVOS!$C$96:$AF$96,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$96:$XFD$96,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33317,7 +33317,7 @@
         <v>108</v>
       </c>
       <c r="C119" t="str">
-        <f>INDEX(NORMATIVOS!$C$97:$AF$97,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$97:$XFD$97,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33329,7 +33329,7 @@
         <v>127</v>
       </c>
       <c r="C120" t="str">
-        <f>INDEX(NORMATIVOS!$C$98:$AF$98,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$98:$XFD$98,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33341,7 +33341,7 @@
         <v>128</v>
       </c>
       <c r="C121" t="str">
-        <f>INDEX(NORMATIVOS!$C$99:$AF$99,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$99:$XFD$99,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33353,7 +33353,7 @@
         <v>129</v>
       </c>
       <c r="C122" t="str">
-        <f>INDEX(NORMATIVOS!$C$100:$AF$100,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$100:$XFD$100,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33365,7 +33365,7 @@
         <v>130</v>
       </c>
       <c r="C123" t="str">
-        <f>INDEX(NORMATIVOS!$C$101:$AF$101,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$101:$XFD$101,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33377,7 +33377,7 @@
         <v>356</v>
       </c>
       <c r="C124" t="str">
-        <f>INDEX(NORMATIVOS!$C$102:$AF$102,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$102:$XFD$102,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33389,7 +33389,7 @@
         <v>131</v>
       </c>
       <c r="C125" t="str">
-        <f>INDEX(NORMATIVOS!$C$103:$AF$103,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$103:$XFD$103,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33401,7 +33401,7 @@
         <v>132</v>
       </c>
       <c r="C126" t="str">
-        <f>INDEX(NORMATIVOS!$C$104:$AF$104,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$104:$XFD$104,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33413,7 +33413,7 @@
         <v>133</v>
       </c>
       <c r="C127" t="str">
-        <f>INDEX(NORMATIVOS!$C$105:$AF$105,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$105:$XFD$105,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33425,7 +33425,7 @@
         <v>136</v>
       </c>
       <c r="C128" t="str">
-        <f>INDEX(NORMATIVOS!$C$108:$AF$108,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$108:$XFD$108,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33437,7 +33437,7 @@
         <v>137</v>
       </c>
       <c r="C129" t="str">
-        <f>INDEX(NORMATIVOS!$C$109:$AF$109,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$109:$XFD$109,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33449,7 +33449,7 @@
         <v>138</v>
       </c>
       <c r="C130" t="str">
-        <f>INDEX(NORMATIVOS!$C$110:$AF$110,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$110:$XFD$110,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33461,7 +33461,7 @@
         <v>328</v>
       </c>
       <c r="C131" t="str">
-        <f>INDEX(NORMATIVOS!$C$111:$AF$111,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$111:$XFD$111,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33473,7 +33473,7 @@
         <v>140</v>
       </c>
       <c r="C132" t="str">
-        <f>INDEX(NORMATIVOS!$C$112:$AF$112,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$112:$XFD$112,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33485,7 +33485,7 @@
         <v>141</v>
       </c>
       <c r="C133" t="str">
-        <f>INDEX(NORMATIVOS!$C$113:$AF$113,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$113:$XFD$113,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33497,7 +33497,7 @@
         <v>142</v>
       </c>
       <c r="C134" t="str">
-        <f>INDEX(NORMATIVOS!$C$114:$AF$114,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$114:$XFD$114,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33509,7 +33509,7 @@
         <v>35</v>
       </c>
       <c r="C135" t="str">
-        <f>INDEX(NORMATIVOS!$C$115:$AF$115,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$115:$XFD$115,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33521,7 +33521,7 @@
         <v>143</v>
       </c>
       <c r="C136" t="str">
-        <f>INDEX(NORMATIVOS!$C$116:$AF$116,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$116:$XFD$116,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -33533,7 +33533,7 @@
         <v>329</v>
       </c>
       <c r="C137" t="str">
-        <f>INDEX(NORMATIVOS!$C$117:$AF$117,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$117:$XFD$117,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -33545,7 +33545,7 @@
         <v>145</v>
       </c>
       <c r="C138" t="str">
-        <f>INDEX(NORMATIVOS!$C$118:$AF$118,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$118:$XFD$118,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -33557,7 +33557,7 @@
         <v>146</v>
       </c>
       <c r="C139" t="str">
-        <f>INDEX(NORMATIVOS!$C$119:$AF$119,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$119:$XFD$119,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33569,7 +33569,7 @@
         <v>147</v>
       </c>
       <c r="C140" t="str">
-        <f>INDEX(NORMATIVOS!$C$120:$AF$120,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$120:$XFD$120,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33581,7 +33581,7 @@
         <v>148</v>
       </c>
       <c r="C141" t="str">
-        <f>INDEX(NORMATIVOS!$C$121:$AF$121,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$121:$XFD$121,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33593,7 +33593,7 @@
         <v>149</v>
       </c>
       <c r="C142" t="str">
-        <f>INDEX(NORMATIVOS!$C$122:$AF$122,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$122:$XFD$122,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33605,7 +33605,7 @@
         <v>151</v>
       </c>
       <c r="C143" t="str">
-        <f>INDEX(NORMATIVOS!$C$123:$AF$123,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$123:$XFD$123,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33617,7 +33617,7 @@
         <v>330</v>
       </c>
       <c r="C144" t="str">
-        <f>INDEX(NORMATIVOS!$C$124:$AF$124,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$124:$XFD$124,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33629,7 +33629,7 @@
         <v>153</v>
       </c>
       <c r="C145" t="str">
-        <f>INDEX(NORMATIVOS!$C$125:$AF$125,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$125:$XFD$125,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33641,7 +33641,7 @@
         <v>154</v>
       </c>
       <c r="C146" t="str">
-        <f>INDEX(NORMATIVOS!$C$126:$AF$126,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$126:$XFD$126,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33653,7 +33653,7 @@
         <v>155</v>
       </c>
       <c r="C147" t="str">
-        <f>INDEX(NORMATIVOS!$C$127:$AF$127,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$127:$XFD$127,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33665,7 +33665,7 @@
         <v>156</v>
       </c>
       <c r="C148" t="str">
-        <f>INDEX(NORMATIVOS!$C$128:$AF$128,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$128:$XFD$128,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33677,7 +33677,7 @@
         <v>157</v>
       </c>
       <c r="C149" t="str">
-        <f>INDEX(NORMATIVOS!$C$129:$AF$129,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$129:$XFD$129,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33689,7 +33689,7 @@
         <v>331</v>
       </c>
       <c r="C150" t="str">
-        <f>INDEX(NORMATIVOS!$C$130:$AF$130,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$130:$XFD$130,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33701,7 +33701,7 @@
         <v>159</v>
       </c>
       <c r="C151" t="str">
-        <f>INDEX(NORMATIVOS!$C$131:$AF$131,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$131:$XFD$131,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -33713,7 +33713,7 @@
         <v>160</v>
       </c>
       <c r="C152" t="str">
-        <f>INDEX(NORMATIVOS!$C$132:$AF$132,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$132:$XFD$132,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -33725,7 +33725,7 @@
         <v>161</v>
       </c>
       <c r="C153" t="str">
-        <f>INDEX(NORMATIVOS!$C$133:$AF$133,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$133:$XFD$133,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -33737,7 +33737,7 @@
         <v>332</v>
       </c>
       <c r="C154" t="str">
-        <f>INDEX(NORMATIVOS!$C$134:$AF$134,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$134:$XFD$134,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33749,7 +33749,7 @@
         <v>333</v>
       </c>
       <c r="C155" t="str">
-        <f>INDEX(NORMATIVOS!$C$135:$AF$135,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$135:$XFD$135,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33761,7 +33761,7 @@
         <v>164</v>
       </c>
       <c r="C156" t="str">
-        <f>INDEX(NORMATIVOS!$C$136:$AF$136,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$136:$XFD$136,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -33773,7 +33773,7 @@
         <v>165</v>
       </c>
       <c r="C157" t="str">
-        <f>INDEX(NORMATIVOS!$C$137:$AF$137,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$137:$XFD$137,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33785,7 +33785,7 @@
         <v>166</v>
       </c>
       <c r="C158" t="str">
-        <f>INDEX(NORMATIVOS!$C$138:$AF$138,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$138:$XFD$138,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33797,7 +33797,7 @@
         <v>167</v>
       </c>
       <c r="C159" t="str">
-        <f>INDEX(NORMATIVOS!$C$139:$AF$139,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$139:$XFD$139,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33809,7 +33809,7 @@
         <v>168</v>
       </c>
       <c r="C160" t="str">
-        <f>INDEX(NORMATIVOS!$C$140:$AF$140,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$140:$XFD$140,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -33821,7 +33821,7 @@
         <v>169</v>
       </c>
       <c r="C161" t="str">
-        <f>INDEX(NORMATIVOS!$C$141:$AF$141,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$141:$XFD$141,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33833,7 +33833,7 @@
         <v>170</v>
       </c>
       <c r="C162" t="str">
-        <f>INDEX(NORMATIVOS!$C$142:$AF$142,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$142:$XFD$142,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -33845,7 +33845,7 @@
         <v>173</v>
       </c>
       <c r="C163" t="str">
-        <f>INDEX(NORMATIVOS!$C$145:$AF$145,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$145:$XFD$145,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33857,7 +33857,7 @@
         <v>334</v>
       </c>
       <c r="C164" t="str">
-        <f>INDEX(NORMATIVOS!$C$146:$AF$146,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$146:$XFD$146,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33869,7 +33869,7 @@
         <v>335</v>
       </c>
       <c r="C165" t="str">
-        <f>INDEX(NORMATIVOS!$C$147:$AF$147,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$147:$XFD$147,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33881,7 +33881,7 @@
         <v>176</v>
       </c>
       <c r="C166" t="str">
-        <f>INDEX(NORMATIVOS!$C$148:$AF$148,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$148:$XFD$148,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33893,7 +33893,7 @@
         <v>177</v>
       </c>
       <c r="C167" t="str">
-        <f>INDEX(NORMATIVOS!$C$149:$AF$149,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$149:$XFD$149,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33905,7 +33905,7 @@
         <v>178</v>
       </c>
       <c r="C168" t="str">
-        <f>INDEX(NORMATIVOS!$C$150:$AF$150,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$150:$XFD$150,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33917,7 +33917,7 @@
         <v>179</v>
       </c>
       <c r="C169" t="str">
-        <f>INDEX(NORMATIVOS!$C$151:$AF$151,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$151:$XFD$151,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33929,7 +33929,7 @@
         <v>181</v>
       </c>
       <c r="C170" t="str">
-        <f>INDEX(NORMATIVOS!$C$152:$AF$152,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$152:$XFD$152,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33941,7 +33941,7 @@
         <v>51</v>
       </c>
       <c r="C171" t="str">
-        <f>INDEX(NORMATIVOS!$C$153:$AF$153,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$153:$XFD$153,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33953,7 +33953,7 @@
         <v>182</v>
       </c>
       <c r="C172" t="str">
-        <f>INDEX(NORMATIVOS!$C$154:$AF$154,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$154:$XFD$154,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33965,7 +33965,7 @@
         <v>183</v>
       </c>
       <c r="C173" t="str">
-        <f>INDEX(NORMATIVOS!$C$155:$AF$155,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$155:$XFD$155,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -33977,7 +33977,7 @@
         <v>184</v>
       </c>
       <c r="C174" t="str">
-        <f>INDEX(NORMATIVOS!$C$156:$AF$156,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$156:$XFD$156,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -33989,7 +33989,7 @@
         <v>185</v>
       </c>
       <c r="C175" t="str">
-        <f>INDEX(NORMATIVOS!$C$157:$AF$157,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$157:$XFD$157,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -34001,7 +34001,7 @@
         <v>186</v>
       </c>
       <c r="C176" t="str">
-        <f>INDEX(NORMATIVOS!$C$158:$AF$158,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$158:$XFD$158,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -34013,7 +34013,7 @@
         <v>187</v>
       </c>
       <c r="C177" t="str">
-        <f>INDEX(NORMATIVOS!$C$159:$AF$159,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$159:$XFD$159,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34025,7 +34025,7 @@
         <v>336</v>
       </c>
       <c r="C178" t="str">
-        <f>INDEX(NORMATIVOS!$C$160:$AF$160,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$160:$XFD$160,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34037,7 +34037,7 @@
         <v>189</v>
       </c>
       <c r="C179" t="str">
-        <f>INDEX(NORMATIVOS!$C$161:$AF$161,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$161:$XFD$161,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34049,7 +34049,7 @@
         <v>190</v>
       </c>
       <c r="C180" t="str">
-        <f>INDEX(NORMATIVOS!$C$162:$AF$162,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$162:$XFD$162,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34061,7 +34061,7 @@
         <v>191</v>
       </c>
       <c r="C181" t="str">
-        <f>INDEX(NORMATIVOS!$C$163:$AF$163,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$163:$XFD$163,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34073,7 +34073,7 @@
         <v>192</v>
       </c>
       <c r="C182" t="str">
-        <f>INDEX(NORMATIVOS!$C$164:$AF$164,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$164:$XFD$164,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34085,7 +34085,7 @@
         <v>193</v>
       </c>
       <c r="C183" t="str">
-        <f>INDEX(NORMATIVOS!$C$165:$AF$165,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$165:$XFD$165,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34097,7 +34097,7 @@
         <v>194</v>
       </c>
       <c r="C184" t="str">
-        <f>INDEX(NORMATIVOS!$C$166:$AF$166,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$166:$XFD$166,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34109,7 +34109,7 @@
         <v>195</v>
       </c>
       <c r="C185" t="str">
-        <f>INDEX(NORMATIVOS!$C$167:$AF$167,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$167:$XFD$167,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34121,7 +34121,7 @@
         <v>196</v>
       </c>
       <c r="C186" t="str">
-        <f>INDEX(NORMATIVOS!$C$168:$AF$168,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$168:$XFD$168,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34133,7 +34133,7 @@
         <v>197</v>
       </c>
       <c r="C187" t="str">
-        <f>INDEX(NORMATIVOS!$C$169:$AF$169,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$169:$XFD$169,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34145,7 +34145,7 @@
         <v>198</v>
       </c>
       <c r="C188" t="str">
-        <f>INDEX(NORMATIVOS!$C$170:$AF$170,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$170:$XFD$170,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34157,7 +34157,7 @@
         <v>199</v>
       </c>
       <c r="C189" t="str">
-        <f>INDEX(NORMATIVOS!$C$171:$AF$171,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$171:$XFD$171,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34169,7 +34169,7 @@
         <v>200</v>
       </c>
       <c r="C190" t="str">
-        <f>INDEX(NORMATIVOS!$C$172:$AF$172,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$172:$XFD$172,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34181,7 +34181,7 @@
         <v>201</v>
       </c>
       <c r="C191" t="str">
-        <f>INDEX(NORMATIVOS!$C$173:$AF$173,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$173:$XFD$173,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34193,7 +34193,7 @@
         <v>204</v>
       </c>
       <c r="C192" t="str">
-        <f>INDEX(NORMATIVOS!$C$176:$AF$176,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$176:$XFD$176,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34205,7 +34205,7 @@
         <v>337</v>
       </c>
       <c r="C193" t="str">
-        <f>INDEX(NORMATIVOS!$C$177:$AF$177,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$177:$XFD$177,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34217,7 +34217,7 @@
         <v>338</v>
       </c>
       <c r="C194" t="str">
-        <f>INDEX(NORMATIVOS!$C$178:$AF$178,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$178:$XFD$178,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34229,7 +34229,7 @@
         <v>207</v>
       </c>
       <c r="C195" t="str">
-        <f>INDEX(NORMATIVOS!$C$179:$AF$179,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$179:$XFD$179,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34241,7 +34241,7 @@
         <v>208</v>
       </c>
       <c r="C196" t="str">
-        <f>INDEX(NORMATIVOS!$C$180:$AF$180,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$180:$XFD$180,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34253,7 +34253,7 @@
         <v>154</v>
       </c>
       <c r="C197" t="str">
-        <f>INDEX(NORMATIVOS!$C$181:$AF$181,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$181:$XFD$181,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>N/A</v>
       </c>
     </row>
@@ -34265,7 +34265,7 @@
         <v>209</v>
       </c>
       <c r="C198" t="str">
-        <f>INDEX(NORMATIVOS!$C$182:$AF$182,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$182:$XFD$182,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -34277,7 +34277,7 @@
         <v>210</v>
       </c>
       <c r="C199" t="str">
-        <f>INDEX(NORMATIVOS!$C$183:$AF$183,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$183:$XFD$183,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>N/A</v>
       </c>
     </row>
@@ -34289,7 +34289,7 @@
         <v>211</v>
       </c>
       <c r="C200" t="str">
-        <f>INDEX(NORMATIVOS!$C$184:$AF$184,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$184:$XFD$184,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34301,7 +34301,7 @@
         <v>212</v>
       </c>
       <c r="C201" t="str">
-        <f>INDEX(NORMATIVOS!$C$185:$AF$185,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$185:$XFD$185,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34313,7 +34313,7 @@
         <v>213</v>
       </c>
       <c r="C202" t="str">
-        <f>INDEX(NORMATIVOS!$C$186:$AF$186,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$186:$XFD$186,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>N/A</v>
       </c>
     </row>
@@ -34325,7 +34325,7 @@
         <v>214</v>
       </c>
       <c r="C203" t="str">
-        <f>INDEX(NORMATIVOS!$C$187:$AF$187,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$187:$XFD$187,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -34337,7 +34337,7 @@
         <v>165</v>
       </c>
       <c r="C204" t="str">
-        <f>INDEX(NORMATIVOS!$C$188:$AF$188,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$188:$XFD$188,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34349,7 +34349,7 @@
         <v>215</v>
       </c>
       <c r="C205" t="str">
-        <f>INDEX(NORMATIVOS!$C$189:$AF$189,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$189:$XFD$189,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34361,7 +34361,7 @@
         <v>216</v>
       </c>
       <c r="C206" t="str">
-        <f>INDEX(NORMATIVOS!$C$190:$AF$190,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$190:$XFD$190,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34373,7 +34373,7 @@
         <v>217</v>
       </c>
       <c r="C207" t="str">
-        <f>INDEX(NORMATIVOS!$C$191:$AF$191,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$191:$XFD$191,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34385,7 +34385,7 @@
         <v>218</v>
       </c>
       <c r="C208" t="str">
-        <f>INDEX(NORMATIVOS!$C$192:$AF$192,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$192:$XFD$192,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34397,7 +34397,7 @@
         <v>219</v>
       </c>
       <c r="C209" t="str">
-        <f>INDEX(NORMATIVOS!$C$193:$AF$193,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$193:$XFD$193,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34409,7 +34409,7 @@
         <v>221</v>
       </c>
       <c r="C210" t="str">
-        <f>INDEX(NORMATIVOS!$C$194:$AF$194,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$194:$XFD$194,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34421,7 +34421,7 @@
         <v>142</v>
       </c>
       <c r="C211" t="str">
-        <f>INDEX(NORMATIVOS!$C$195:$AF$195,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$195:$XFD$195,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34433,7 +34433,7 @@
         <v>43</v>
       </c>
       <c r="C212" t="str">
-        <f>INDEX(NORMATIVOS!$C$196:$AF$196,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$196:$XFD$196,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34445,7 +34445,7 @@
         <v>204</v>
       </c>
       <c r="C213" t="str">
-        <f>INDEX(NORMATIVOS!$C$197:$AF$197,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$197:$XFD$197,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34457,7 +34457,7 @@
         <v>337</v>
       </c>
       <c r="C214" t="str">
-        <f>INDEX(NORMATIVOS!$C$198:$AF$198,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$198:$XFD$198,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34469,7 +34469,7 @@
         <v>223</v>
       </c>
       <c r="C215" t="str">
-        <f>INDEX(NORMATIVOS!$C$199:$AF$199,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$199:$XFD$199,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34481,7 +34481,7 @@
         <v>224</v>
       </c>
       <c r="C216" t="str">
-        <f>INDEX(NORMATIVOS!$C$200:$AF$200,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$200:$XFD$200,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34493,7 +34493,7 @@
         <v>225</v>
       </c>
       <c r="C217" t="str">
-        <f>INDEX(NORMATIVOS!$C$201:$AF$201,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$201:$XFD$201,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34505,7 +34505,7 @@
         <v>226</v>
       </c>
       <c r="C218" t="str">
-        <f>INDEX(NORMATIVOS!$C$202:$AF$202,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$202:$XFD$202,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34517,7 +34517,7 @@
         <v>227</v>
       </c>
       <c r="C219" t="str">
-        <f>INDEX(NORMATIVOS!$C$203:$AF$203,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$203:$XFD$203,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34529,7 +34529,7 @@
         <v>228</v>
       </c>
       <c r="C220" t="str">
-        <f>INDEX(NORMATIVOS!$C$204:$AF$204,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$204:$XFD$204,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34541,7 +34541,7 @@
         <v>229</v>
       </c>
       <c r="C221" t="str">
-        <f>INDEX(NORMATIVOS!$C$205:$AF$205,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$205:$XFD$205,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -34553,7 +34553,7 @@
         <v>339</v>
       </c>
       <c r="C222" t="str">
-        <f>INDEX(NORMATIVOS!$C$206:$AF$206,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$206:$XFD$206,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34565,7 +34565,7 @@
         <v>340</v>
       </c>
       <c r="C223" t="str">
-        <f>INDEX(NORMATIVOS!$C$207:$AF$207,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$207:$XFD$207,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>N/A</v>
       </c>
     </row>
@@ -34577,7 +34577,7 @@
         <v>357</v>
       </c>
       <c r="C224" t="str">
-        <f>INDEX(NORMATIVOS!$C$208:$AF$208,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$208:$XFD$208,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -34589,7 +34589,7 @@
         <v>232</v>
       </c>
       <c r="C225" t="str">
-        <f>INDEX(NORMATIVOS!$C$209:$AF$209,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$209:$XFD$209,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -34601,7 +34601,7 @@
         <v>233</v>
       </c>
       <c r="C226" t="str">
-        <f>INDEX(NORMATIVOS!$C$210:$AF$210,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$210:$XFD$210,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34613,7 +34613,7 @@
         <v>234</v>
       </c>
       <c r="C227" t="str">
-        <f>INDEX(NORMATIVOS!$C$211:$AF$211,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$211:$XFD$211,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -34625,7 +34625,7 @@
         <v>235</v>
       </c>
       <c r="C228" t="str">
-        <f>INDEX(NORMATIVOS!$C$212:$AF$212,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$212:$XFD$212,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34637,7 +34637,7 @@
         <v>341</v>
       </c>
       <c r="C229" t="str">
-        <f>INDEX(NORMATIVOS!$C$213:$AF$213,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$213:$XFD$213,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34649,7 +34649,7 @@
         <v>237</v>
       </c>
       <c r="C230" t="str">
-        <f>INDEX(NORMATIVOS!$C$214:$AF$214,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$214:$XFD$214,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34661,7 +34661,7 @@
         <v>238</v>
       </c>
       <c r="C231" t="str">
-        <f>INDEX(NORMATIVOS!$C$215:$AF$215,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$215:$XFD$215,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34673,7 +34673,7 @@
         <v>239</v>
       </c>
       <c r="C232" t="str">
-        <f>INDEX(NORMATIVOS!$C$216:$AF$216,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$216:$XFD$216,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34685,7 +34685,7 @@
         <v>240</v>
       </c>
       <c r="C233" t="str">
-        <f>INDEX(NORMATIVOS!$C$217:$AF$217,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$217:$XFD$217,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34697,7 +34697,7 @@
         <v>241</v>
       </c>
       <c r="C234" t="str">
-        <f>INDEX(NORMATIVOS!$C$218:$AF$218,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$218:$XFD$218,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34709,7 +34709,7 @@
         <v>204</v>
       </c>
       <c r="C235" t="str">
-        <f>INDEX(NORMATIVOS!$C$219:$AF$219,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$219:$XFD$219,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34721,7 +34721,7 @@
         <v>337</v>
       </c>
       <c r="C236" t="str">
-        <f>INDEX(NORMATIVOS!$C$220:$AF$220,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$220:$XFD$220,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34733,7 +34733,7 @@
         <v>338</v>
       </c>
       <c r="C237" t="str">
-        <f>INDEX(NORMATIVOS!$C$221:$AF$221,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$221:$XFD$221,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34745,7 +34745,7 @@
         <v>161</v>
       </c>
       <c r="C238" t="str">
-        <f>INDEX(NORMATIVOS!$C$222:$AF$222,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$222:$XFD$222,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34757,7 +34757,7 @@
         <v>243</v>
       </c>
       <c r="C239" t="str">
-        <f>INDEX(NORMATIVOS!$C$223:$AF$223,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$223:$XFD$223,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34769,7 +34769,7 @@
         <v>244</v>
       </c>
       <c r="C240" t="str">
-        <f>INDEX(NORMATIVOS!$C$224:$AF$224,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$224:$XFD$224,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34781,7 +34781,7 @@
         <v>245</v>
       </c>
       <c r="C241" t="str">
-        <f>INDEX(NORMATIVOS!$C$225:$AF$225,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$225:$XFD$225,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -34793,7 +34793,7 @@
         <v>246</v>
       </c>
       <c r="C242" t="str">
-        <f>INDEX(NORMATIVOS!$C$226:$AF$226,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$226:$XFD$226,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -34805,7 +34805,7 @@
         <v>342</v>
       </c>
       <c r="C243" t="str">
-        <f>INDEX(NORMATIVOS!$C$227:$AF$227,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$227:$XFD$227,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34817,7 +34817,7 @@
         <v>248</v>
       </c>
       <c r="C244" t="str">
-        <f>INDEX(NORMATIVOS!$C$228:$AF$228,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$228:$XFD$228,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34829,7 +34829,7 @@
         <v>249</v>
       </c>
       <c r="C245" t="str">
-        <f>INDEX(NORMATIVOS!$C$229:$AF$229,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$229:$XFD$229,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34841,7 +34841,7 @@
         <v>250</v>
       </c>
       <c r="C246" t="str">
-        <f>INDEX(NORMATIVOS!$C$230:$AF$230,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$230:$XFD$230,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34853,7 +34853,7 @@
         <v>343</v>
       </c>
       <c r="C247" t="str">
-        <f>INDEX(NORMATIVOS!$C$231:$AF$231,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$231:$XFD$231,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -34865,7 +34865,7 @@
         <v>254</v>
       </c>
       <c r="C248" t="str">
-        <f>INDEX(NORMATIVOS!$C$234:$AF$234,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$234:$XFD$234,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34877,7 +34877,7 @@
         <v>255</v>
       </c>
       <c r="C249" t="str">
-        <f>INDEX(NORMATIVOS!$C$235:$AF$235,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$235:$XFD$235,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34889,7 +34889,7 @@
         <v>151</v>
       </c>
       <c r="C250" t="str">
-        <f>INDEX(NORMATIVOS!$C$236:$AF$236,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$236:$XFD$236,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34901,7 +34901,7 @@
         <v>330</v>
       </c>
       <c r="C251" t="str">
-        <f>INDEX(NORMATIVOS!$C$237:$AF$237,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$237:$XFD$237,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34913,7 +34913,7 @@
         <v>256</v>
       </c>
       <c r="C252" t="str">
-        <f>INDEX(NORMATIVOS!$C$238:$AF$238,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$238:$XFD$238,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34925,7 +34925,7 @@
         <v>257</v>
       </c>
       <c r="C253" t="str">
-        <f>INDEX(NORMATIVOS!$C$239:$AF$239,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$239:$XFD$239,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34937,7 +34937,7 @@
         <v>258</v>
       </c>
       <c r="C254" t="str">
-        <f>INDEX(NORMATIVOS!$C$240:$AF$240,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$240:$XFD$240,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34949,7 +34949,7 @@
         <v>259</v>
       </c>
       <c r="C255" t="str">
-        <f>INDEX(NORMATIVOS!$C$241:$AF$241,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$241:$XFD$241,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34961,7 +34961,7 @@
         <v>260</v>
       </c>
       <c r="C256" t="str">
-        <f>INDEX(NORMATIVOS!$C$242:$AF$242,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$242:$XFD$242,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34973,7 +34973,7 @@
         <v>165</v>
       </c>
       <c r="C257" t="str">
-        <f>INDEX(NORMATIVOS!$C$243:$AF$243,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$243:$XFD$243,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34985,7 +34985,7 @@
         <v>164</v>
       </c>
       <c r="C258" t="str">
-        <f>INDEX(NORMATIVOS!$C$244:$AF$244,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$244:$XFD$244,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -34997,7 +34997,7 @@
         <v>262</v>
       </c>
       <c r="C259" t="str">
-        <f>INDEX(NORMATIVOS!$C$245:$AF$245,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$245:$XFD$245,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -35009,7 +35009,7 @@
         <v>228</v>
       </c>
       <c r="C260" t="str">
-        <f>INDEX(NORMATIVOS!$C$246:$AF$246,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$246:$XFD$246,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -35021,7 +35021,7 @@
         <v>263</v>
       </c>
       <c r="C261" t="str">
-        <f>INDEX(NORMATIVOS!$C$247:$AF$247,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$247:$XFD$247,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -35033,7 +35033,7 @@
         <v>264</v>
       </c>
       <c r="C262" t="str">
-        <f>INDEX(NORMATIVOS!$C$248:$AF$248,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$248:$XFD$248,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -35045,7 +35045,7 @@
         <v>265</v>
       </c>
       <c r="C263" t="str">
-        <f>INDEX(NORMATIVOS!$C$249:$AF$249,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$249:$XFD$249,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -35057,7 +35057,7 @@
         <v>266</v>
       </c>
       <c r="C264" t="str">
-        <f>INDEX(NORMATIVOS!$C$250:$AF$250,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$250:$XFD$250,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -35069,7 +35069,7 @@
         <v>267</v>
       </c>
       <c r="C265" t="str">
-        <f>INDEX(NORMATIVOS!$C$251:$AF$251,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$251:$XFD$251,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35081,7 +35081,7 @@
         <v>268</v>
       </c>
       <c r="C266" t="str">
-        <f>INDEX(NORMATIVOS!$C$252:$AF$252,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$252:$XFD$252,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35093,7 +35093,7 @@
         <v>269</v>
       </c>
       <c r="C267" t="str">
-        <f>INDEX(NORMATIVOS!$C$253:$AF$253,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$253:$XFD$253,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35105,7 +35105,7 @@
         <v>270</v>
       </c>
       <c r="C268" t="str">
-        <f>INDEX(NORMATIVOS!$C$254:$AF$254,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$254:$XFD$254,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35117,7 +35117,7 @@
         <v>271</v>
       </c>
       <c r="C269" t="str">
-        <f>INDEX(NORMATIVOS!$C$255:$AF$255,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$255:$XFD$255,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35129,7 +35129,7 @@
         <v>272</v>
       </c>
       <c r="C270" t="str">
-        <f>INDEX(NORMATIVOS!$C$256:$AF$256,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$256:$XFD$256,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35141,7 +35141,7 @@
         <v>273</v>
       </c>
       <c r="C271" t="str">
-        <f>INDEX(NORMATIVOS!$C$257:$AF$257,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$257:$XFD$257,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35153,7 +35153,7 @@
         <v>274</v>
       </c>
       <c r="C272" t="str">
-        <f>INDEX(NORMATIVOS!$C$258:$AF$258,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$258:$XFD$258,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35165,7 +35165,7 @@
         <v>275</v>
       </c>
       <c r="C273" t="str">
-        <f>INDEX(NORMATIVOS!$C$259:$AF$259,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$259:$XFD$259,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35177,7 +35177,7 @@
         <v>276</v>
       </c>
       <c r="C274" t="str">
-        <f>INDEX(NORMATIVOS!$C$260:$AF$260,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$260:$XFD$260,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35189,7 +35189,7 @@
         <v>277</v>
       </c>
       <c r="C275" t="str">
-        <f>INDEX(NORMATIVOS!$C$261:$AF$261,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$261:$XFD$261,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35201,7 +35201,7 @@
         <v>344</v>
       </c>
       <c r="C276" t="str">
-        <f>INDEX(NORMATIVOS!$C$262:$AF$262,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$262:$XFD$262,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -35213,7 +35213,7 @@
         <v>280</v>
       </c>
       <c r="C277" t="str">
-        <f>INDEX(NORMATIVOS!$C$263:$AF$263,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$263:$XFD$263,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -35225,7 +35225,7 @@
         <v>345</v>
       </c>
       <c r="C278" t="str">
-        <f>INDEX(NORMATIVOS!$C$264:$AF$264,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$264:$XFD$264,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -35237,7 +35237,7 @@
         <v>358</v>
       </c>
       <c r="C279" t="str">
-        <f>INDEX(NORMATIVOS!$C$265:$AF$265,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$265:$XFD$265,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -35249,7 +35249,7 @@
         <v>282</v>
       </c>
       <c r="C280" t="str">
-        <f>INDEX(NORMATIVOS!$C$266:$AF$266,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$266:$XFD$266,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -35261,7 +35261,7 @@
         <v>283</v>
       </c>
       <c r="C281" t="str">
-        <f>INDEX(NORMATIVOS!$C$267:$AF$267,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$267:$XFD$267,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -35273,7 +35273,7 @@
         <v>346</v>
       </c>
       <c r="C282" t="str">
-        <f>INDEX(NORMATIVOS!$C$268:$AF$268,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$268:$XFD$268,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -35285,7 +35285,7 @@
         <v>285</v>
       </c>
       <c r="C283" t="str">
-        <f>INDEX(NORMATIVOS!$C$269:$AF$269,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$269:$XFD$269,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Consolidado</v>
       </c>
     </row>
@@ -35297,7 +35297,7 @@
         <v>286</v>
       </c>
       <c r="C284" t="str">
-        <f>INDEX(NORMATIVOS!$C$270:$AF$270,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$270:$XFD$270,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -35309,7 +35309,7 @@
         <v>347</v>
       </c>
       <c r="C285" t="str">
-        <f>INDEX(NORMATIVOS!$C$271:$AF$271,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$271:$XFD$271,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -35321,7 +35321,7 @@
         <v>288</v>
       </c>
       <c r="C286" t="str">
-        <f>INDEX(NORMATIVOS!$C$272:$AF$272,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$272:$XFD$272,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>En proceso</v>
       </c>
     </row>
@@ -35333,7 +35333,7 @@
         <v>289</v>
       </c>
       <c r="C287" t="str">
-        <f>INDEX(NORMATIVOS!$C$273:$AF$273,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$273:$XFD$273,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35345,7 +35345,7 @@
         <v>290</v>
       </c>
       <c r="C288" t="str">
-        <f>INDEX(NORMATIVOS!$C$274:$AF$274,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$274:$XFD$274,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35357,7 +35357,7 @@
         <v>291</v>
       </c>
       <c r="C289" t="str">
-        <f>INDEX(NORMATIVOS!$C$275:$AF$275,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$275:$XFD$275,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35369,7 +35369,7 @@
         <v>292</v>
       </c>
       <c r="C290" t="str">
-        <f>INDEX(NORMATIVOS!$C$276:$AF$276,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$276:$XFD$276,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35381,7 +35381,7 @@
         <v>293</v>
       </c>
       <c r="C291" t="str">
-        <f>INDEX(NORMATIVOS!$C$277:$AF$277,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$277:$XFD$277,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35393,7 +35393,7 @@
         <v>294</v>
       </c>
       <c r="C292" t="str">
-        <f>INDEX(NORMATIVOS!$C$278:$AF$278,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$278:$XFD$278,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35405,7 +35405,7 @@
         <v>295</v>
       </c>
       <c r="C293" t="str">
-        <f>INDEX(NORMATIVOS!$C$279:$AF$279,1,MATCH($B$3,NORMATIVOS!$C$1:$AF$1,0))</f>
+        <f>INDEX(NORMATIVOS!$C$279:$XFD$279,1,MATCH($B$3,NORMATIVOS!$C$1:$XFD$1,0))</f>
         <v>Proyección</v>
       </c>
     </row>
@@ -35435,7 +35435,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0300-000000000000}">
           <x14:formula1>
-            <xm:f>CONSOLIDADO!$A$4:$A$33</xm:f>
+            <xm:f>CONSOLIDADO!$A$4:$A$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>B3</xm:sqref>
         </x14:dataValidation>
@@ -35478,7 +35478,7 @@
         <v>349</v>
       </c>
       <c r="B3" s="14">
-        <f>COUNTA(CONSOLIDADO!A4:A33)</f>
+        <f>COUNTA(CONSOLIDADO!A4:A1048576)</f>
         <v>30</v>
       </c>
       <c r="D3" s="11" t="s">
@@ -35493,14 +35493,14 @@
         <v>351</v>
       </c>
       <c r="B4" s="15">
-        <f>AVERAGE(CONSOLIDADO!G4:G33)</f>
+        <f>AVERAGE(CONSOLIDADO!G4:G1048576)</f>
         <v>0.40337869202570076</v>
       </c>
       <c r="D4" t="s">
         <v>299</v>
       </c>
       <c r="E4">
-        <f>SUM(CONSOLIDADO!F4:F33)</f>
+        <f>SUM(CONSOLIDADO!F4:F1048576)</f>
         <v>98</v>
       </c>
     </row>
@@ -35509,14 +35509,14 @@
         <v>352</v>
       </c>
       <c r="B5" s="14">
-        <f>SUM(CONSOLIDADO!C4:C33)</f>
+        <f>SUM(CONSOLIDADO!C4:C1048576)</f>
         <v>3170</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
       </c>
       <c r="E5">
-        <f>SUM(CONSOLIDADO!E4:E33)</f>
+        <f>SUM(CONSOLIDADO!E4:E1048576)</f>
         <v>3676</v>
       </c>
     </row>
@@ -35525,14 +35525,14 @@
         <v>353</v>
       </c>
       <c r="B6" s="14">
-        <f>SUM(CONSOLIDADO!D4:D33)</f>
+        <f>SUM(CONSOLIDADO!D4:D1048576)</f>
         <v>1066</v>
       </c>
       <c r="D6" t="s">
         <v>303</v>
       </c>
       <c r="E6">
-        <f>SUM(CONSOLIDADO!D4:D33)</f>
+        <f>SUM(CONSOLIDADO!D4:D1048576)</f>
         <v>1066</v>
       </c>
     </row>
@@ -35541,7 +35541,7 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <f>SUM(CONSOLIDADO!C4:C33)</f>
+        <f>SUM(CONSOLIDADO!C4:C1048576)</f>
         <v>3170</v>
       </c>
     </row>
